--- a/data/nzd0253/nzd0253.xlsx
+++ b/data/nzd0253/nzd0253.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W405"/>
+  <dimension ref="A1:W406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30827,6 +30827,81 @@
       <c r="W405" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:53:47+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>345.39</v>
+      </c>
+      <c r="C406" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="D406" t="n">
+        <v>326.61</v>
+      </c>
+      <c r="E406" t="n">
+        <v>327.63</v>
+      </c>
+      <c r="F406" t="n">
+        <v>323.82</v>
+      </c>
+      <c r="G406" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="H406" t="n">
+        <v>328.61</v>
+      </c>
+      <c r="I406" t="n">
+        <v>331.52</v>
+      </c>
+      <c r="J406" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="K406" t="n">
+        <v>343.95</v>
+      </c>
+      <c r="L406" t="n">
+        <v>343.71</v>
+      </c>
+      <c r="M406" t="n">
+        <v>349.56</v>
+      </c>
+      <c r="N406" t="n">
+        <v>345.23</v>
+      </c>
+      <c r="O406" t="n">
+        <v>348.91</v>
+      </c>
+      <c r="P406" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>348.2</v>
+      </c>
+      <c r="R406" t="n">
+        <v>341.72</v>
+      </c>
+      <c r="S406" t="n">
+        <v>334.29</v>
+      </c>
+      <c r="T406" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="U406" t="n">
+        <v>337.44</v>
+      </c>
+      <c r="V406" t="n">
+        <v>342.28</v>
+      </c>
+      <c r="W406" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -30841,7 +30916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B407"/>
+  <dimension ref="A1:B408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34914,6 +34989,16 @@
       </c>
       <c r="B407" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -35082,28 +35167,28 @@
         <v>0.0723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2054746150944826</v>
+        <v>0.2053171009958503</v>
       </c>
       <c r="J2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L2" t="n">
-        <v>0.131503865905076</v>
+        <v>0.1320358760367339</v>
       </c>
       <c r="M2" t="n">
-        <v>3.150569209252766</v>
+        <v>3.143465567964613</v>
       </c>
       <c r="N2" t="n">
-        <v>15.21034771822273</v>
+        <v>15.17300979263563</v>
       </c>
       <c r="O2" t="n">
-        <v>3.900044579004544</v>
+        <v>3.895254778911853</v>
       </c>
       <c r="P2" t="n">
-        <v>340.2583600292205</v>
+        <v>340.2599449584059</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35160,28 +35245,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2428680004206955</v>
+        <v>0.2412984969393595</v>
       </c>
       <c r="J3" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K3" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1508712850553462</v>
+        <v>0.1498532880409161</v>
       </c>
       <c r="M3" t="n">
-        <v>3.425757625518757</v>
+        <v>3.424015737136852</v>
       </c>
       <c r="N3" t="n">
-        <v>18.10927044005957</v>
+        <v>18.086248928948</v>
       </c>
       <c r="O3" t="n">
-        <v>4.255498847380831</v>
+        <v>4.252793073845469</v>
       </c>
       <c r="P3" t="n">
-        <v>329.8446300530717</v>
+        <v>329.8604226195511</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35238,28 +35323,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2595399595988827</v>
+        <v>0.2558494542146129</v>
       </c>
       <c r="J4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1632278684852415</v>
+        <v>0.1593313138375065</v>
       </c>
       <c r="M4" t="n">
-        <v>3.431824415445011</v>
+        <v>3.44418297313658</v>
       </c>
       <c r="N4" t="n">
-        <v>18.83713219383856</v>
+        <v>18.91056004492665</v>
       </c>
       <c r="O4" t="n">
-        <v>4.340176516437846</v>
+        <v>4.348627374807671</v>
       </c>
       <c r="P4" t="n">
-        <v>326.7518435681143</v>
+        <v>326.7889779563566</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35316,28 +35401,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1999263717043451</v>
+        <v>0.1983540101339688</v>
       </c>
       <c r="J5" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K5" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0837460750119835</v>
+        <v>0.08294330587515819</v>
       </c>
       <c r="M5" t="n">
-        <v>3.850546706135505</v>
+        <v>3.849023618285957</v>
       </c>
       <c r="N5" t="n">
-        <v>23.85530518729488</v>
+        <v>23.81817501359089</v>
       </c>
       <c r="O5" t="n">
-        <v>4.88418930706979</v>
+        <v>4.880386768852536</v>
       </c>
       <c r="P5" t="n">
-        <v>325.3269521451037</v>
+        <v>325.34277347008</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35394,28 +35479,28 @@
         <v>0.0835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2081326839248128</v>
+        <v>0.2056784598240259</v>
       </c>
       <c r="J6" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K6" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08898451122383733</v>
+        <v>0.08739874429431005</v>
       </c>
       <c r="M6" t="n">
-        <v>4.030553994653094</v>
+        <v>4.033245998784277</v>
       </c>
       <c r="N6" t="n">
-        <v>24.19275529017888</v>
+        <v>24.18606188724298</v>
       </c>
       <c r="O6" t="n">
-        <v>4.918613147034322</v>
+        <v>4.917932684293572</v>
       </c>
       <c r="P6" t="n">
-        <v>322.9726582831806</v>
+        <v>322.9973530339267</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35472,28 +35557,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2277849804627956</v>
+        <v>0.226773504599629</v>
       </c>
       <c r="J7" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K7" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08705311717147557</v>
+        <v>0.08681446129418435</v>
       </c>
       <c r="M7" t="n">
-        <v>4.51492436796263</v>
+        <v>4.509531917978379</v>
       </c>
       <c r="N7" t="n">
-        <v>29.68279372843841</v>
+        <v>29.6185123826251</v>
       </c>
       <c r="O7" t="n">
-        <v>5.448191785210797</v>
+        <v>5.442289259367339</v>
       </c>
       <c r="P7" t="n">
-        <v>323.0066148798207</v>
+        <v>323.0167924933153</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35550,28 +35635,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1483461828687304</v>
+        <v>0.1474701573211766</v>
       </c>
       <c r="J8" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K8" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04433128720373081</v>
+        <v>0.04408161992800219</v>
       </c>
       <c r="M8" t="n">
-        <v>4.05495113925579</v>
+        <v>4.049858639015401</v>
       </c>
       <c r="N8" t="n">
-        <v>25.87874433206776</v>
+        <v>25.82160427786624</v>
       </c>
       <c r="O8" t="n">
-        <v>5.087115521793049</v>
+        <v>5.081496263687128</v>
       </c>
       <c r="P8" t="n">
-        <v>326.3464677080015</v>
+        <v>326.3552824012226</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35628,28 +35713,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2067589829283701</v>
+        <v>0.2062035567804271</v>
       </c>
       <c r="J9" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K9" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1028179391241111</v>
+        <v>0.1028811069582073</v>
       </c>
       <c r="M9" t="n">
-        <v>3.461512922589368</v>
+        <v>3.456162129950658</v>
       </c>
       <c r="N9" t="n">
-        <v>20.34856945375586</v>
+        <v>20.30104277702914</v>
       </c>
       <c r="O9" t="n">
-        <v>4.510938866107128</v>
+        <v>4.505667850278041</v>
       </c>
       <c r="P9" t="n">
-        <v>327.1091367467939</v>
+        <v>327.1147255234166</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35706,28 +35791,28 @@
         <v>0.0864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1906550165415953</v>
+        <v>0.1923329391480744</v>
       </c>
       <c r="J10" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K10" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05298606534482919</v>
+        <v>0.05415323122935101</v>
       </c>
       <c r="M10" t="n">
-        <v>4.543619324915132</v>
+        <v>4.537170071962906</v>
       </c>
       <c r="N10" t="n">
-        <v>35.43925588685656</v>
+        <v>35.37654481121088</v>
       </c>
       <c r="O10" t="n">
-        <v>5.953087928701924</v>
+        <v>5.947818491784268</v>
       </c>
       <c r="P10" t="n">
-        <v>331.0504825688284</v>
+        <v>331.0335990737455</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35784,28 +35869,28 @@
         <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1254882182468521</v>
+        <v>0.1276724321061388</v>
       </c>
       <c r="J11" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K11" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L11" t="n">
-        <v>0.017053308957102</v>
+        <v>0.01773448547691403</v>
       </c>
       <c r="M11" t="n">
-        <v>5.520594208077408</v>
+        <v>5.514732479989547</v>
       </c>
       <c r="N11" t="n">
-        <v>49.51315863934634</v>
+        <v>49.43291657887055</v>
       </c>
       <c r="O11" t="n">
-        <v>7.036558721374131</v>
+        <v>7.030854612269446</v>
       </c>
       <c r="P11" t="n">
-        <v>336.4863130857232</v>
+        <v>336.4643352162964</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35862,28 +35947,28 @@
         <v>0.1196</v>
       </c>
       <c r="I12" t="n">
-        <v>0.134424377502034</v>
+        <v>0.1354498377092417</v>
       </c>
       <c r="J12" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K12" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02157664804372605</v>
+        <v>0.02202855294889483</v>
       </c>
       <c r="M12" t="n">
-        <v>5.3223466745612</v>
+        <v>5.312284892427163</v>
       </c>
       <c r="N12" t="n">
-        <v>44.69843542828645</v>
+        <v>44.59732927116826</v>
       </c>
       <c r="O12" t="n">
-        <v>6.685688852189164</v>
+        <v>6.678123184785397</v>
       </c>
       <c r="P12" t="n">
-        <v>338.2145784511512</v>
+        <v>338.204260125205</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35940,28 +36025,28 @@
         <v>0.0833</v>
       </c>
       <c r="I13" t="n">
-        <v>0.16105748048449</v>
+        <v>0.1617067006077312</v>
       </c>
       <c r="J13" t="n">
+        <v>405</v>
+      </c>
+      <c r="K13" t="n">
         <v>404</v>
       </c>
-      <c r="K13" t="n">
-        <v>403</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.03443072390446</v>
+        <v>0.03490413392264557</v>
       </c>
       <c r="M13" t="n">
-        <v>4.959220037717282</v>
+        <v>4.94902882984381</v>
       </c>
       <c r="N13" t="n">
-        <v>39.77426015501587</v>
+        <v>39.67953167214343</v>
       </c>
       <c r="O13" t="n">
-        <v>6.306683768432968</v>
+        <v>6.299169125538973</v>
       </c>
       <c r="P13" t="n">
-        <v>344.0754866235544</v>
+        <v>344.0689593297921</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36018,28 +36103,28 @@
         <v>0.0706</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07048091336326406</v>
+        <v>0.06952053676192503</v>
       </c>
       <c r="J14" t="n">
+        <v>405</v>
+      </c>
+      <c r="K14" t="n">
         <v>404</v>
       </c>
-      <c r="K14" t="n">
-        <v>403</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.007253138071286247</v>
+        <v>0.007100204383616138</v>
       </c>
       <c r="M14" t="n">
-        <v>4.844748370418087</v>
+        <v>4.838928050895694</v>
       </c>
       <c r="N14" t="n">
-        <v>37.17565669009976</v>
+        <v>37.09178388251625</v>
       </c>
       <c r="O14" t="n">
-        <v>6.097184324760057</v>
+        <v>6.090302445898418</v>
       </c>
       <c r="P14" t="n">
-        <v>345.1870583249117</v>
+        <v>345.1967140025086</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36096,28 +36181,28 @@
         <v>0.1594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06476045618049152</v>
+        <v>0.06336735597695024</v>
       </c>
       <c r="J15" t="n">
+        <v>405</v>
+      </c>
+      <c r="K15" t="n">
         <v>404</v>
       </c>
-      <c r="K15" t="n">
-        <v>403</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.007414486041440127</v>
+        <v>0.007141003545199864</v>
       </c>
       <c r="M15" t="n">
-        <v>4.344890145151416</v>
+        <v>4.341292732727533</v>
       </c>
       <c r="N15" t="n">
-        <v>30.69797324324191</v>
+        <v>30.63912906353525</v>
       </c>
       <c r="O15" t="n">
-        <v>5.540575172600938</v>
+        <v>5.535262330146174</v>
       </c>
       <c r="P15" t="n">
-        <v>349.8375759658686</v>
+        <v>349.8515822696529</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36174,28 +36259,28 @@
         <v>0.1171</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01587933524827214</v>
+        <v>-0.01853587715495422</v>
       </c>
       <c r="J16" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K16" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0005945156341892188</v>
+        <v>0.0008127433167925968</v>
       </c>
       <c r="M16" t="n">
-        <v>3.884079140013872</v>
+        <v>3.887873930274947</v>
       </c>
       <c r="N16" t="n">
-        <v>23.1225914528193</v>
+        <v>23.12764605735897</v>
       </c>
       <c r="O16" t="n">
-        <v>4.808595580085655</v>
+        <v>4.809121131491592</v>
       </c>
       <c r="P16" t="n">
-        <v>360.6602025905028</v>
+        <v>360.686933091687</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36252,28 +36337,28 @@
         <v>0.0732</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.00937305606230799</v>
+        <v>-0.01233344563471145</v>
       </c>
       <c r="J17" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K17" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0001857137501348749</v>
+        <v>0.0003225392584678133</v>
       </c>
       <c r="M17" t="n">
-        <v>4.200572972990521</v>
+        <v>4.204905606944641</v>
       </c>
       <c r="N17" t="n">
-        <v>25.80067863693096</v>
+        <v>25.81415019019431</v>
       </c>
       <c r="O17" t="n">
-        <v>5.079436842498483</v>
+        <v>5.080762756731937</v>
       </c>
       <c r="P17" t="n">
-        <v>354.0628480015845</v>
+        <v>354.0926358610463</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36330,28 +36415,28 @@
         <v>0.1014</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04182863790139631</v>
+        <v>0.04004326931910686</v>
       </c>
       <c r="J18" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K18" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L18" t="n">
-        <v>0.006297817292015284</v>
+        <v>0.005799632700007717</v>
       </c>
       <c r="M18" t="n">
-        <v>3.262276311266124</v>
+        <v>3.261779087172422</v>
       </c>
       <c r="N18" t="n">
-        <v>15.05937866596085</v>
+        <v>15.05026521824289</v>
       </c>
       <c r="O18" t="n">
-        <v>3.880641527629272</v>
+        <v>3.879467130707888</v>
       </c>
       <c r="P18" t="n">
-        <v>343.9972156303853</v>
+        <v>344.0151802621056</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36408,28 +36493,28 @@
         <v>0.1035</v>
       </c>
       <c r="I19" t="n">
-        <v>0.05644557871723001</v>
+        <v>0.05507379850789502</v>
       </c>
       <c r="J19" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K19" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01188756291962745</v>
+        <v>0.01137980832029695</v>
       </c>
       <c r="M19" t="n">
-        <v>3.134436365362075</v>
+        <v>3.133135310495995</v>
       </c>
       <c r="N19" t="n">
-        <v>14.51414662994052</v>
+        <v>14.49480075140632</v>
       </c>
       <c r="O19" t="n">
-        <v>3.809743643598677</v>
+        <v>3.807203796936318</v>
       </c>
       <c r="P19" t="n">
-        <v>335.4008963351153</v>
+        <v>335.4146769908321</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36486,28 +36571,28 @@
         <v>0.1228</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1607175039579795</v>
+        <v>0.1599486080896703</v>
       </c>
       <c r="J20" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K20" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08873032594056862</v>
+        <v>0.08842663501083603</v>
       </c>
       <c r="M20" t="n">
-        <v>3.117079521543502</v>
+        <v>3.112703733186855</v>
       </c>
       <c r="N20" t="n">
-        <v>14.53849019189857</v>
+        <v>14.50765156636508</v>
       </c>
       <c r="O20" t="n">
-        <v>3.81293721321222</v>
+        <v>3.808891120308518</v>
       </c>
       <c r="P20" t="n">
-        <v>334.4352410186949</v>
+        <v>334.4429652074323</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36564,28 +36649,28 @@
         <v>0.1003</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3506099677652659</v>
+        <v>0.348881879025649</v>
       </c>
       <c r="J21" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K21" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2999975664181868</v>
+        <v>0.2988696257068474</v>
       </c>
       <c r="M21" t="n">
-        <v>3.225621703809812</v>
+        <v>3.225548216856455</v>
       </c>
       <c r="N21" t="n">
-        <v>15.71985170848427</v>
+        <v>15.70729808084487</v>
       </c>
       <c r="O21" t="n">
-        <v>3.964826819482065</v>
+        <v>3.963243378956795</v>
       </c>
       <c r="P21" t="n">
-        <v>331.4503059357143</v>
+        <v>331.4676660024412</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36642,28 +36727,28 @@
         <v>0.1131</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2983769124405172</v>
+        <v>0.2976130464097806</v>
       </c>
       <c r="J22" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K22" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L22" t="n">
-        <v>0.204561780785593</v>
+        <v>0.204691805649706</v>
       </c>
       <c r="M22" t="n">
-        <v>3.578563393010999</v>
+        <v>3.573553639542475</v>
       </c>
       <c r="N22" t="n">
-        <v>18.88451395476683</v>
+        <v>18.84302388108899</v>
       </c>
       <c r="O22" t="n">
-        <v>4.345631594459754</v>
+        <v>4.340855201580558</v>
       </c>
       <c r="P22" t="n">
-        <v>335.8374160810323</v>
+        <v>335.8451022092984</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36701,7 +36786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W405"/>
+  <dimension ref="A1:W406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84053,6 +84138,123 @@
         </is>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:53:47+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>-38.27445913115451,178.3304366310709</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>-38.27516120310996,178.330626055454</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>-38.275844406569036,178.33087245743664</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>-38.27650080623734,178.3311998079156</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>-38.27717272695948,178.3314757907181</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>-38.27782034188824,178.33181799565696</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>-38.27847931447836,178.33212868906836</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>-38.279135690772016,178.33245521792006</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>-38.27978046597606,178.33283480127233</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>-38.280422204043084,178.33322809892266</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>-38.28105804050449,178.3336294508071</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>-38.28166828988138,178.33409189732774</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>-38.28227436742267,178.33456984318877</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>-38.28282669806634,178.33512879844648</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>-38.283366168911634,178.33571093878712</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>-38.28388955689503,178.33632523925013</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>-38.28439791232054,178.33695312982044</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>-38.28492668376582,178.3375468809148</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>-38.28541081585631,178.3382111302783</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>-38.28585875694743,178.3389321008365</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>-38.28618730986033,178.33974329269367</t>
+        </is>
+      </c>
+      <c r="W406" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0253/nzd0253.xlsx
+++ b/data/nzd0253/nzd0253.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W406"/>
+  <dimension ref="A1:W407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30902,6 +30902,81 @@
       <c r="W406" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>339.63</v>
+      </c>
+      <c r="C407" t="n">
+        <v>332.04</v>
+      </c>
+      <c r="D407" t="n">
+        <v>326.96</v>
+      </c>
+      <c r="E407" t="n">
+        <v>324.52</v>
+      </c>
+      <c r="F407" t="n">
+        <v>321.12</v>
+      </c>
+      <c r="G407" t="n">
+        <v>325.56</v>
+      </c>
+      <c r="H407" t="n">
+        <v>331.39</v>
+      </c>
+      <c r="I407" t="n">
+        <v>334.24</v>
+      </c>
+      <c r="J407" t="n">
+        <v>338.45</v>
+      </c>
+      <c r="K407" t="n">
+        <v>341.47</v>
+      </c>
+      <c r="L407" t="n">
+        <v>342.74</v>
+      </c>
+      <c r="M407" t="n">
+        <v>348.27</v>
+      </c>
+      <c r="N407" t="n">
+        <v>347.61</v>
+      </c>
+      <c r="O407" t="n">
+        <v>348.97</v>
+      </c>
+      <c r="P407" t="n">
+        <v>353.79</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>349.38</v>
+      </c>
+      <c r="R407" t="n">
+        <v>342.48</v>
+      </c>
+      <c r="S407" t="n">
+        <v>335.87</v>
+      </c>
+      <c r="T407" t="n">
+        <v>339.26</v>
+      </c>
+      <c r="U407" t="n">
+        <v>340.23</v>
+      </c>
+      <c r="V407" t="n">
+        <v>340.9</v>
+      </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -30916,7 +30991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B408"/>
+  <dimension ref="A1:B409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34999,6 +35074,16 @@
       </c>
       <c r="B408" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -35167,28 +35252,28 @@
         <v>0.0723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2053171009958503</v>
+        <v>0.202110760188166</v>
       </c>
       <c r="J2" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K2" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1320358760367339</v>
+        <v>0.1285038249372853</v>
       </c>
       <c r="M2" t="n">
-        <v>3.143465567964613</v>
+        <v>3.149506359297411</v>
       </c>
       <c r="N2" t="n">
-        <v>15.17300979263563</v>
+        <v>15.2258341002463</v>
       </c>
       <c r="O2" t="n">
-        <v>3.895254778911853</v>
+        <v>3.902029484799712</v>
       </c>
       <c r="P2" t="n">
-        <v>340.2599449584059</v>
+        <v>340.2923469678927</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35245,28 +35330,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2412984969393595</v>
+        <v>0.2390664571704162</v>
       </c>
       <c r="J3" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K3" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1498532880409161</v>
+        <v>0.147982459822706</v>
       </c>
       <c r="M3" t="n">
-        <v>3.424015737136852</v>
+        <v>3.425065454731211</v>
       </c>
       <c r="N3" t="n">
-        <v>18.086248928948</v>
+        <v>18.08541073084852</v>
       </c>
       <c r="O3" t="n">
-        <v>4.252793073845469</v>
+        <v>4.252694525926889</v>
       </c>
       <c r="P3" t="n">
-        <v>329.8604226195511</v>
+        <v>329.882978728869</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35323,28 +35408,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2558494542146129</v>
+        <v>0.2523577238657767</v>
       </c>
       <c r="J4" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K4" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1593313138375065</v>
+        <v>0.1557620934589871</v>
       </c>
       <c r="M4" t="n">
-        <v>3.44418297313658</v>
+        <v>3.455298192900407</v>
       </c>
       <c r="N4" t="n">
-        <v>18.91056004492665</v>
+        <v>18.970949485814</v>
       </c>
       <c r="O4" t="n">
-        <v>4.348627374807671</v>
+        <v>4.355565346291339</v>
       </c>
       <c r="P4" t="n">
-        <v>326.7889779563566</v>
+        <v>326.8242639994425</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35401,28 +35486,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1983540101339688</v>
+        <v>0.1951400278659974</v>
       </c>
       <c r="J5" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K5" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08294330587515819</v>
+        <v>0.08067239557140093</v>
       </c>
       <c r="M5" t="n">
-        <v>3.849023618285957</v>
+        <v>3.855740774807536</v>
       </c>
       <c r="N5" t="n">
-        <v>23.81817501359089</v>
+        <v>23.85013624064742</v>
       </c>
       <c r="O5" t="n">
-        <v>4.880386768852536</v>
+        <v>4.883660127470729</v>
       </c>
       <c r="P5" t="n">
-        <v>325.34277347008</v>
+        <v>325.375252701136</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35479,28 +35564,28 @@
         <v>0.0835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2056784598240259</v>
+        <v>0.2018087287295175</v>
       </c>
       <c r="J6" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K6" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08739874429431005</v>
+        <v>0.08447892046758276</v>
       </c>
       <c r="M6" t="n">
-        <v>4.033245998784277</v>
+        <v>4.04308673442249</v>
       </c>
       <c r="N6" t="n">
-        <v>24.18606188724298</v>
+        <v>24.25787074419868</v>
       </c>
       <c r="O6" t="n">
-        <v>4.917932684293572</v>
+        <v>4.925227989057834</v>
       </c>
       <c r="P6" t="n">
-        <v>322.9973530339267</v>
+        <v>323.0364590027417</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35557,28 +35642,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.226773504599629</v>
+        <v>0.2249372374251705</v>
       </c>
       <c r="J7" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K7" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08681446129418435</v>
+        <v>0.08594506530063928</v>
       </c>
       <c r="M7" t="n">
-        <v>4.509531917978379</v>
+        <v>4.508759645221843</v>
       </c>
       <c r="N7" t="n">
-        <v>29.6185123826251</v>
+        <v>29.57514329032745</v>
       </c>
       <c r="O7" t="n">
-        <v>5.442289259367339</v>
+        <v>5.438303346663135</v>
       </c>
       <c r="P7" t="n">
-        <v>323.0167924933153</v>
+        <v>323.0353490816431</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35635,28 +35720,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1474701573211766</v>
+        <v>0.1480609805881684</v>
       </c>
       <c r="J8" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K8" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04408161992800219</v>
+        <v>0.04468057944394077</v>
       </c>
       <c r="M8" t="n">
-        <v>4.049858639015401</v>
+        <v>4.042069814823472</v>
       </c>
       <c r="N8" t="n">
-        <v>25.82160427786624</v>
+        <v>25.7610668252459</v>
       </c>
       <c r="O8" t="n">
-        <v>5.081496263687128</v>
+        <v>5.07553611210145</v>
       </c>
       <c r="P8" t="n">
-        <v>326.3552824012226</v>
+        <v>326.3493117754375</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35713,28 +35798,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2062035567804271</v>
+        <v>0.2070726124804174</v>
       </c>
       <c r="J9" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K9" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1028811069582073</v>
+        <v>0.1042111856612506</v>
       </c>
       <c r="M9" t="n">
-        <v>3.456162129950658</v>
+        <v>3.45075315803711</v>
       </c>
       <c r="N9" t="n">
-        <v>20.30104277702914</v>
+        <v>20.25766640579797</v>
       </c>
       <c r="O9" t="n">
-        <v>4.505667850278041</v>
+        <v>4.500851742259233</v>
       </c>
       <c r="P9" t="n">
-        <v>327.1147255234166</v>
+        <v>327.1059431909309</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35791,28 +35876,28 @@
         <v>0.0864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1923329391480744</v>
+        <v>0.1935540471011756</v>
       </c>
       <c r="J10" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K10" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05415323122935101</v>
+        <v>0.05511033290202916</v>
       </c>
       <c r="M10" t="n">
-        <v>4.537170071962906</v>
+        <v>4.529469882560123</v>
       </c>
       <c r="N10" t="n">
-        <v>35.37654481121088</v>
+        <v>35.30249255793803</v>
       </c>
       <c r="O10" t="n">
-        <v>5.947818491784268</v>
+        <v>5.941590069832993</v>
       </c>
       <c r="P10" t="n">
-        <v>331.0335990737455</v>
+        <v>331.0212590407128</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35869,28 +35954,28 @@
         <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1276724321061388</v>
+        <v>0.1285230729186147</v>
       </c>
       <c r="J11" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K11" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01773448547691403</v>
+        <v>0.01807556692324241</v>
       </c>
       <c r="M11" t="n">
-        <v>5.514732479989547</v>
+        <v>5.504134390429704</v>
       </c>
       <c r="N11" t="n">
-        <v>49.43291657887055</v>
+        <v>49.31750898693519</v>
       </c>
       <c r="O11" t="n">
-        <v>7.030854612269446</v>
+        <v>7.022642592851724</v>
       </c>
       <c r="P11" t="n">
-        <v>336.4643352162964</v>
+        <v>336.4557389773658</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35947,28 +36032,28 @@
         <v>0.1196</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1354498377092417</v>
+        <v>0.1359457638323099</v>
       </c>
       <c r="J12" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K12" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02202855294889483</v>
+        <v>0.02232139618189366</v>
       </c>
       <c r="M12" t="n">
-        <v>5.312284892427163</v>
+        <v>5.300668485844962</v>
       </c>
       <c r="N12" t="n">
-        <v>44.59732927116826</v>
+        <v>44.48964139238993</v>
       </c>
       <c r="O12" t="n">
-        <v>6.678123184785397</v>
+        <v>6.670055576409385</v>
       </c>
       <c r="P12" t="n">
-        <v>338.204260125205</v>
+        <v>338.1992484923474</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36025,28 +36110,28 @@
         <v>0.0833</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1617067006077312</v>
+        <v>0.1616604678786444</v>
       </c>
       <c r="J13" t="n">
+        <v>406</v>
+      </c>
+      <c r="K13" t="n">
         <v>405</v>
       </c>
-      <c r="K13" t="n">
-        <v>404</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.03490413392264557</v>
+        <v>0.03509559043271149</v>
       </c>
       <c r="M13" t="n">
-        <v>4.94902882984381</v>
+        <v>4.937091763902361</v>
       </c>
       <c r="N13" t="n">
-        <v>39.67953167214343</v>
+        <v>39.58157632790302</v>
       </c>
       <c r="O13" t="n">
-        <v>6.299169125538973</v>
+        <v>6.291389061876798</v>
       </c>
       <c r="P13" t="n">
-        <v>344.0689593297921</v>
+        <v>344.0694261717238</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36103,28 +36188,28 @@
         <v>0.0706</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06952053676192503</v>
+        <v>0.06982210603188017</v>
       </c>
       <c r="J14" t="n">
+        <v>406</v>
+      </c>
+      <c r="K14" t="n">
         <v>405</v>
       </c>
-      <c r="K14" t="n">
-        <v>404</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.007100204383616138</v>
+        <v>0.007205851816596831</v>
       </c>
       <c r="M14" t="n">
-        <v>4.838928050895694</v>
+        <v>4.827860748922424</v>
       </c>
       <c r="N14" t="n">
-        <v>37.09178388251625</v>
+        <v>37.00099946784405</v>
       </c>
       <c r="O14" t="n">
-        <v>6.090302445898418</v>
+        <v>6.08284468549412</v>
       </c>
       <c r="P14" t="n">
-        <v>345.1967140025086</v>
+        <v>345.1936688614724</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36181,28 +36266,28 @@
         <v>0.1594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06336735597695024</v>
+        <v>0.06201412567811018</v>
       </c>
       <c r="J15" t="n">
+        <v>406</v>
+      </c>
+      <c r="K15" t="n">
         <v>405</v>
       </c>
-      <c r="K15" t="n">
-        <v>404</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.007141003545199864</v>
+        <v>0.006880260577173059</v>
       </c>
       <c r="M15" t="n">
-        <v>4.341292732727533</v>
+        <v>4.33745179072755</v>
       </c>
       <c r="N15" t="n">
-        <v>30.63912906353525</v>
+        <v>30.57959031662123</v>
       </c>
       <c r="O15" t="n">
-        <v>5.535262330146174</v>
+        <v>5.529881582513429</v>
       </c>
       <c r="P15" t="n">
-        <v>349.8515822696529</v>
+        <v>349.8652467160172</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36259,28 +36344,28 @@
         <v>0.1171</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01853587715495422</v>
+        <v>-0.02191685801353216</v>
       </c>
       <c r="J16" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K16" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0008127433167925968</v>
+        <v>0.001138074286179402</v>
       </c>
       <c r="M16" t="n">
-        <v>3.887873930274947</v>
+        <v>3.895194418336394</v>
       </c>
       <c r="N16" t="n">
-        <v>23.12764605735897</v>
+        <v>23.17097070148184</v>
       </c>
       <c r="O16" t="n">
-        <v>4.809121131491592</v>
+        <v>4.813623448243728</v>
       </c>
       <c r="P16" t="n">
-        <v>360.686933091687</v>
+        <v>360.721099944316</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36337,28 +36422,28 @@
         <v>0.0732</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.01233344563471145</v>
+        <v>-0.01464791385361309</v>
       </c>
       <c r="J17" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K17" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0003225392584678133</v>
+        <v>0.0004569062950927627</v>
       </c>
       <c r="M17" t="n">
-        <v>4.204905606944641</v>
+        <v>4.206058819476648</v>
       </c>
       <c r="N17" t="n">
-        <v>25.81415019019431</v>
+        <v>25.79756569509989</v>
       </c>
       <c r="O17" t="n">
-        <v>5.080762756731937</v>
+        <v>5.079130407372889</v>
       </c>
       <c r="P17" t="n">
-        <v>354.0926358610463</v>
+        <v>354.1160249596119</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36415,28 +36500,28 @@
         <v>0.1014</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04004326931910686</v>
+        <v>0.03867260985056573</v>
       </c>
       <c r="J18" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K18" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005799632700007717</v>
+        <v>0.005439279470255465</v>
       </c>
       <c r="M18" t="n">
-        <v>3.261779087172422</v>
+        <v>3.259477930139542</v>
       </c>
       <c r="N18" t="n">
-        <v>15.05026521824289</v>
+        <v>15.02967829636029</v>
       </c>
       <c r="O18" t="n">
-        <v>3.879467130707888</v>
+        <v>3.876812904482275</v>
       </c>
       <c r="P18" t="n">
-        <v>344.0151802621056</v>
+        <v>344.029031603484</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36493,28 +36578,28 @@
         <v>0.1035</v>
       </c>
       <c r="I19" t="n">
-        <v>0.05507379850789502</v>
+        <v>0.05454297997719696</v>
       </c>
       <c r="J19" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K19" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01137980832029695</v>
+        <v>0.01123109216247253</v>
       </c>
       <c r="M19" t="n">
-        <v>3.133135310495995</v>
+        <v>3.127858989963741</v>
       </c>
       <c r="N19" t="n">
-        <v>14.49480075140632</v>
+        <v>14.4614091778102</v>
       </c>
       <c r="O19" t="n">
-        <v>3.807203796936318</v>
+        <v>3.802815953712486</v>
       </c>
       <c r="P19" t="n">
-        <v>335.4146769908321</v>
+        <v>335.4200327116473</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36571,28 +36656,28 @@
         <v>0.1228</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1599486080896703</v>
+        <v>0.1602486440936361</v>
       </c>
       <c r="J20" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K20" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08842663501083603</v>
+        <v>0.08923037285790114</v>
       </c>
       <c r="M20" t="n">
-        <v>3.112703733186855</v>
+        <v>3.106495225957266</v>
       </c>
       <c r="N20" t="n">
-        <v>14.50765156636508</v>
+        <v>14.47253599139985</v>
       </c>
       <c r="O20" t="n">
-        <v>3.808891120308518</v>
+        <v>3.804278642712683</v>
       </c>
       <c r="P20" t="n">
-        <v>334.4429652074323</v>
+        <v>334.4399379787679</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36649,28 +36734,28 @@
         <v>0.1003</v>
       </c>
       <c r="I21" t="n">
-        <v>0.348881879025649</v>
+        <v>0.3486197305666439</v>
       </c>
       <c r="J21" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K21" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2988696257068474</v>
+        <v>0.2998543840765681</v>
       </c>
       <c r="M21" t="n">
-        <v>3.225548216856455</v>
+        <v>3.218753419243521</v>
       </c>
       <c r="N21" t="n">
-        <v>15.70729808084487</v>
+        <v>15.66902511009643</v>
       </c>
       <c r="O21" t="n">
-        <v>3.963243378956795</v>
+        <v>3.958411942950913</v>
       </c>
       <c r="P21" t="n">
-        <v>331.4676660024412</v>
+        <v>331.4703109627758</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36727,28 +36812,28 @@
         <v>0.1131</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2976130464097806</v>
+        <v>0.2961129158792458</v>
       </c>
       <c r="J22" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K22" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L22" t="n">
-        <v>0.204691805649706</v>
+        <v>0.2038934095759917</v>
       </c>
       <c r="M22" t="n">
-        <v>3.573553639542475</v>
+        <v>3.572188478943595</v>
       </c>
       <c r="N22" t="n">
-        <v>18.84302388108899</v>
+        <v>18.81635613253848</v>
       </c>
       <c r="O22" t="n">
-        <v>4.340855201580558</v>
+        <v>4.33778239801612</v>
       </c>
       <c r="P22" t="n">
-        <v>335.8451022092984</v>
+        <v>335.8602619339183</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36786,7 +36871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W406"/>
+  <dimension ref="A1:W407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84255,6 +84340,123 @@
         </is>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>-38.27447917719302,178.33037607805096</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>-38.27516555339671,178.3306129144949</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>-38.27584318848251,178.33087613693522</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>-38.276511629875834,178.33116711269315</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>-38.27718202206713,178.3314473517511</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>-38.277825517739394,178.3318015866408</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>-38.27847021438988,178.33215821154803</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>-38.27912678702098,178.3324841034408</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>-38.279783337561526,178.33282618979382</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>-38.280432187405545,178.33320281433902</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>-38.28106222789502,178.33361974906518</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>-38.2816745871883,178.33407954585002</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>-38.28226134239184,178.3345913723239</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>-38.28282636661518,178.33512933817084</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>-38.28337496252316,178.33569936025154</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>-38.283881378150326,178.336333806471</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>-38.28439268407155,178.33695870773744</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>-38.284916124793945,178.33755892979346</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>-38.28539675832644,178.33822588850722</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>-38.28583758958174,178.33894916116526</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>-38.28619820435784,178.33973576907022</t>
+        </is>
+      </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0253/nzd0253.xlsx
+++ b/data/nzd0253/nzd0253.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W407"/>
+  <dimension ref="A1:W408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30977,6 +30977,81 @@
       <c r="W407" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:53:39+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>340.18</v>
+      </c>
+      <c r="C408" t="n">
+        <v>332.35</v>
+      </c>
+      <c r="D408" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="E408" t="n">
+        <v>323.73</v>
+      </c>
+      <c r="F408" t="n">
+        <v>320.99</v>
+      </c>
+      <c r="G408" t="n">
+        <v>328.71</v>
+      </c>
+      <c r="H408" t="n">
+        <v>333.04</v>
+      </c>
+      <c r="I408" t="n">
+        <v>338.3</v>
+      </c>
+      <c r="J408" t="n">
+        <v>342.84</v>
+      </c>
+      <c r="K408" t="n">
+        <v>345.99</v>
+      </c>
+      <c r="L408" t="n">
+        <v>347.61</v>
+      </c>
+      <c r="M408" t="n">
+        <v>353.28</v>
+      </c>
+      <c r="N408" t="n">
+        <v>350.59</v>
+      </c>
+      <c r="O408" t="n">
+        <v>352.88</v>
+      </c>
+      <c r="P408" t="n">
+        <v>359.69</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>353.79</v>
+      </c>
+      <c r="R408" t="n">
+        <v>346.32</v>
+      </c>
+      <c r="S408" t="n">
+        <v>339.28</v>
+      </c>
+      <c r="T408" t="n">
+        <v>342.04</v>
+      </c>
+      <c r="U408" t="n">
+        <v>343.97</v>
+      </c>
+      <c r="V408" t="n">
+        <v>343.61</v>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -30991,7 +31066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B409"/>
+  <dimension ref="A1:B410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35084,6 +35159,16 @@
       </c>
       <c r="B409" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>-0.62</v>
       </c>
     </row>
   </sheetData>
@@ -35252,28 +35337,28 @@
         <v>0.0723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.202110760188166</v>
+        <v>0.1992396335194262</v>
       </c>
       <c r="J2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1285038249372853</v>
+        <v>0.1254861221436964</v>
       </c>
       <c r="M2" t="n">
-        <v>3.149506359297411</v>
+        <v>3.154159126718568</v>
       </c>
       <c r="N2" t="n">
-        <v>15.2258341002463</v>
+        <v>15.26156072975101</v>
       </c>
       <c r="O2" t="n">
-        <v>3.902029484799712</v>
+        <v>3.906604757298979</v>
       </c>
       <c r="P2" t="n">
-        <v>340.2923469678927</v>
+        <v>340.3213863314922</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35330,28 +35415,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2390664571704162</v>
+        <v>0.2370297685539546</v>
       </c>
       <c r="J3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.147982459822706</v>
+        <v>0.1463570019917254</v>
       </c>
       <c r="M3" t="n">
-        <v>3.425065454731211</v>
+        <v>3.425393670584879</v>
       </c>
       <c r="N3" t="n">
-        <v>18.08541073084852</v>
+        <v>18.0777774731358</v>
       </c>
       <c r="O3" t="n">
-        <v>4.252694525926889</v>
+        <v>4.251796969886474</v>
       </c>
       <c r="P3" t="n">
-        <v>329.882978728869</v>
+        <v>329.9035783568534</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35408,28 +35493,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2523577238657767</v>
+        <v>0.2492867630387995</v>
       </c>
       <c r="J4" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K4" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1557620934589871</v>
+        <v>0.1528002575130897</v>
       </c>
       <c r="M4" t="n">
-        <v>3.455298192900407</v>
+        <v>3.463975939307727</v>
       </c>
       <c r="N4" t="n">
-        <v>18.970949485814</v>
+        <v>19.00800945318594</v>
       </c>
       <c r="O4" t="n">
-        <v>4.355565346291339</v>
+        <v>4.359817594026835</v>
       </c>
       <c r="P4" t="n">
-        <v>326.8242639994425</v>
+        <v>326.8553245405971</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35486,28 +35571,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1951400278659974</v>
+        <v>0.1915603833873838</v>
       </c>
       <c r="J5" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K5" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08067239557140093</v>
+        <v>0.07807146444517543</v>
       </c>
       <c r="M5" t="n">
-        <v>3.855740774807536</v>
+        <v>3.864346350122593</v>
       </c>
       <c r="N5" t="n">
-        <v>23.85013624064742</v>
+        <v>23.90522305621634</v>
       </c>
       <c r="O5" t="n">
-        <v>4.883660127470729</v>
+        <v>4.889296785450474</v>
       </c>
       <c r="P5" t="n">
-        <v>325.375252701136</v>
+        <v>325.4114582084385</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35564,28 +35649,28 @@
         <v>0.0835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2018087287295175</v>
+        <v>0.1979249810866058</v>
       </c>
       <c r="J6" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K6" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08447892046758276</v>
+        <v>0.0815723874416342</v>
       </c>
       <c r="M6" t="n">
-        <v>4.04308673442249</v>
+        <v>4.053220601234132</v>
       </c>
       <c r="N6" t="n">
-        <v>24.25787074419868</v>
+        <v>24.33209239068246</v>
       </c>
       <c r="O6" t="n">
-        <v>4.925227989057834</v>
+        <v>4.932757078012505</v>
       </c>
       <c r="P6" t="n">
-        <v>323.0364590027417</v>
+        <v>323.0757402929611</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35642,28 +35727,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2249372374251705</v>
+        <v>0.2247803053162964</v>
       </c>
       <c r="J7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08594506530063928</v>
+        <v>0.08632253806420742</v>
       </c>
       <c r="M7" t="n">
-        <v>4.508759645221843</v>
+        <v>4.498561194980025</v>
       </c>
       <c r="N7" t="n">
-        <v>29.57514329032745</v>
+        <v>29.50269559154901</v>
       </c>
       <c r="O7" t="n">
-        <v>5.438303346663135</v>
+        <v>5.431638389247669</v>
       </c>
       <c r="P7" t="n">
-        <v>323.0353490816431</v>
+        <v>323.0369363360891</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35720,28 +35805,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1480609805881684</v>
+        <v>0.149506612220869</v>
       </c>
       <c r="J8" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K8" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04468057944394077</v>
+        <v>0.04575599526163565</v>
       </c>
       <c r="M8" t="n">
-        <v>4.042069814823472</v>
+        <v>4.037462676236879</v>
       </c>
       <c r="N8" t="n">
-        <v>25.7610668252459</v>
+        <v>25.71631332638964</v>
       </c>
       <c r="O8" t="n">
-        <v>5.07553611210145</v>
+        <v>5.07112544967975</v>
       </c>
       <c r="P8" t="n">
-        <v>326.3493117754375</v>
+        <v>326.3346902601034</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35798,28 +35883,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2070726124804174</v>
+        <v>0.2100574322950579</v>
       </c>
       <c r="J9" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K9" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1042111856612506</v>
+        <v>0.1071329139232431</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45075315803711</v>
+        <v>3.452943837122695</v>
       </c>
       <c r="N9" t="n">
-        <v>20.25766640579797</v>
+        <v>20.28693673104069</v>
       </c>
       <c r="O9" t="n">
-        <v>4.500851742259233</v>
+        <v>4.50410221143356</v>
       </c>
       <c r="P9" t="n">
-        <v>327.1059431909309</v>
+        <v>327.0757539036312</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35876,28 +35961,28 @@
         <v>0.0864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1935540471011756</v>
+        <v>0.1970533267253037</v>
       </c>
       <c r="J10" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K10" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05511033290202916</v>
+        <v>0.05717428229327537</v>
       </c>
       <c r="M10" t="n">
-        <v>4.529469882560123</v>
+        <v>4.528294562095632</v>
       </c>
       <c r="N10" t="n">
-        <v>35.30249255793803</v>
+        <v>35.3243935592741</v>
       </c>
       <c r="O10" t="n">
-        <v>5.941590069832993</v>
+        <v>5.943432809351352</v>
       </c>
       <c r="P10" t="n">
-        <v>331.0212590407128</v>
+        <v>330.9858663656184</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35954,28 +36039,28 @@
         <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1285230729186147</v>
+        <v>0.1317274978911523</v>
       </c>
       <c r="J11" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K11" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01807556692324241</v>
+        <v>0.01905193660791815</v>
       </c>
       <c r="M11" t="n">
-        <v>5.504134390429704</v>
+        <v>5.501844647655032</v>
       </c>
       <c r="N11" t="n">
-        <v>49.31750898693519</v>
+        <v>49.28743816903048</v>
       </c>
       <c r="O11" t="n">
-        <v>7.022642592851724</v>
+        <v>7.020501276193209</v>
       </c>
       <c r="P11" t="n">
-        <v>336.4557389773658</v>
+        <v>336.4233285431909</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36032,28 +36117,28 @@
         <v>0.1196</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1359457638323099</v>
+        <v>0.138983190504317</v>
       </c>
       <c r="J12" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K12" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02232139618189366</v>
+        <v>0.02340584644160637</v>
       </c>
       <c r="M12" t="n">
-        <v>5.300668485844962</v>
+        <v>5.296592406051601</v>
       </c>
       <c r="N12" t="n">
-        <v>44.48964139238993</v>
+        <v>44.46218449977638</v>
       </c>
       <c r="O12" t="n">
-        <v>6.670055576409385</v>
+        <v>6.667997038074956</v>
       </c>
       <c r="P12" t="n">
-        <v>338.1992484923474</v>
+        <v>338.1685271248453</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36110,28 +36195,28 @@
         <v>0.0833</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1616604678786444</v>
+        <v>0.1642375658850476</v>
       </c>
       <c r="J13" t="n">
+        <v>407</v>
+      </c>
+      <c r="K13" t="n">
         <v>406</v>
       </c>
-      <c r="K13" t="n">
-        <v>405</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.03509559043271149</v>
+        <v>0.03634688022317789</v>
       </c>
       <c r="M13" t="n">
-        <v>4.937091763902361</v>
+        <v>4.933260047043349</v>
       </c>
       <c r="N13" t="n">
-        <v>39.58157632790302</v>
+        <v>39.54318176058321</v>
       </c>
       <c r="O13" t="n">
-        <v>6.291389061876798</v>
+        <v>6.288336963027921</v>
       </c>
       <c r="P13" t="n">
-        <v>344.0694261717238</v>
+        <v>344.0433811219953</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36188,28 +36273,28 @@
         <v>0.0706</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06982210603188017</v>
+        <v>0.07167929591305294</v>
       </c>
       <c r="J14" t="n">
+        <v>407</v>
+      </c>
+      <c r="K14" t="n">
         <v>406</v>
       </c>
-      <c r="K14" t="n">
-        <v>405</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.007205851816596831</v>
+        <v>0.007631850900525983</v>
       </c>
       <c r="M14" t="n">
-        <v>4.827860748922424</v>
+        <v>4.821365548866417</v>
       </c>
       <c r="N14" t="n">
-        <v>37.00099946784405</v>
+        <v>36.94055536464012</v>
       </c>
       <c r="O14" t="n">
-        <v>6.08284468549412</v>
+        <v>6.077874247188742</v>
       </c>
       <c r="P14" t="n">
-        <v>345.1936688614724</v>
+        <v>345.17489945391</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36266,28 +36351,28 @@
         <v>0.1594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06201412567811018</v>
+        <v>0.06272925841530448</v>
       </c>
       <c r="J15" t="n">
+        <v>407</v>
+      </c>
+      <c r="K15" t="n">
         <v>406</v>
       </c>
-      <c r="K15" t="n">
-        <v>405</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.006880260577173059</v>
+        <v>0.007081115209472633</v>
       </c>
       <c r="M15" t="n">
-        <v>4.33745179072755</v>
+        <v>4.329814967955969</v>
       </c>
       <c r="N15" t="n">
-        <v>30.57959031662123</v>
+        <v>30.5088218147959</v>
       </c>
       <c r="O15" t="n">
-        <v>5.529881582513429</v>
+        <v>5.523479140432767</v>
       </c>
       <c r="P15" t="n">
-        <v>349.8652467160172</v>
+        <v>349.8580193355851</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36344,28 +36429,28 @@
         <v>0.1171</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.02191685801353216</v>
+        <v>-0.02215306994081502</v>
       </c>
       <c r="J16" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K16" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001138074286179402</v>
+        <v>0.001169905482966249</v>
       </c>
       <c r="M16" t="n">
-        <v>3.895194418336394</v>
+        <v>3.886799406968577</v>
       </c>
       <c r="N16" t="n">
-        <v>23.17097070148184</v>
+        <v>23.11453460163344</v>
       </c>
       <c r="O16" t="n">
-        <v>4.813623448243728</v>
+        <v>4.807757751970605</v>
       </c>
       <c r="P16" t="n">
-        <v>360.721099944316</v>
+        <v>360.7234890566173</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36422,28 +36507,28 @@
         <v>0.0732</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.01464791385361309</v>
+        <v>-0.01461587700598413</v>
       </c>
       <c r="J17" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K17" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0004569062950927627</v>
+        <v>0.0004577379174542928</v>
       </c>
       <c r="M17" t="n">
-        <v>4.206058819476648</v>
+        <v>4.195863360144211</v>
       </c>
       <c r="N17" t="n">
-        <v>25.79756569509989</v>
+        <v>25.73419011883626</v>
       </c>
       <c r="O17" t="n">
-        <v>5.079130407372889</v>
+        <v>5.072887749481183</v>
       </c>
       <c r="P17" t="n">
-        <v>354.1160249596119</v>
+        <v>354.115700930137</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36500,28 +36585,28 @@
         <v>0.1014</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03867260985056573</v>
+        <v>0.03933570135990321</v>
       </c>
       <c r="J18" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K18" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005439279470255465</v>
+        <v>0.005659668965879772</v>
       </c>
       <c r="M18" t="n">
-        <v>3.259477930139542</v>
+        <v>3.254873242252718</v>
       </c>
       <c r="N18" t="n">
-        <v>15.02967829636029</v>
+        <v>14.99665134610542</v>
       </c>
       <c r="O18" t="n">
-        <v>3.876812904482275</v>
+        <v>3.872551012718285</v>
       </c>
       <c r="P18" t="n">
-        <v>344.029031603484</v>
+        <v>344.0223249138597</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36578,28 +36663,28 @@
         <v>0.1035</v>
       </c>
       <c r="I19" t="n">
-        <v>0.05454297997719696</v>
+        <v>0.0558066518047014</v>
       </c>
       <c r="J19" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K19" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01123109216247253</v>
+        <v>0.01181192915424123</v>
       </c>
       <c r="M19" t="n">
-        <v>3.127858989963741</v>
+        <v>3.126071567033773</v>
       </c>
       <c r="N19" t="n">
-        <v>14.4614091778102</v>
+        <v>14.43995309025057</v>
       </c>
       <c r="O19" t="n">
-        <v>3.802815953712486</v>
+        <v>3.799993827659536</v>
       </c>
       <c r="P19" t="n">
-        <v>335.4200327116473</v>
+        <v>335.4072718045437</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36656,28 +36741,28 @@
         <v>0.1228</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1602486440936361</v>
+        <v>0.1619981713170918</v>
       </c>
       <c r="J20" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K20" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08923037285790114</v>
+        <v>0.09136747703393699</v>
       </c>
       <c r="M20" t="n">
-        <v>3.106495225957266</v>
+        <v>3.107543970850342</v>
       </c>
       <c r="N20" t="n">
-        <v>14.47253599139985</v>
+        <v>14.46411758319737</v>
       </c>
       <c r="O20" t="n">
-        <v>3.804278642712683</v>
+        <v>3.803172042282254</v>
       </c>
       <c r="P20" t="n">
-        <v>334.4399379787679</v>
+        <v>334.4222707696968</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36734,28 +36819,28 @@
         <v>0.1003</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3486197305666439</v>
+        <v>0.3503142482441595</v>
       </c>
       <c r="J21" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K21" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2998543840765681</v>
+        <v>0.3028546588990126</v>
       </c>
       <c r="M21" t="n">
-        <v>3.218753419243521</v>
+        <v>3.218991726645391</v>
       </c>
       <c r="N21" t="n">
-        <v>15.66902511009643</v>
+        <v>15.65596163007208</v>
       </c>
       <c r="O21" t="n">
-        <v>3.958411942950913</v>
+        <v>3.956761507858678</v>
       </c>
       <c r="P21" t="n">
-        <v>331.4703109627758</v>
+        <v>331.4531992552916</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36812,28 +36897,28 @@
         <v>0.1131</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2961129158792458</v>
+        <v>0.2960503428328508</v>
       </c>
       <c r="J22" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K22" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2038934095759917</v>
+        <v>0.2048322800827984</v>
       </c>
       <c r="M22" t="n">
-        <v>3.572188478943595</v>
+        <v>3.563721096177161</v>
       </c>
       <c r="N22" t="n">
-        <v>18.81635613253848</v>
+        <v>18.77015903724898</v>
       </c>
       <c r="O22" t="n">
-        <v>4.33778239801612</v>
+        <v>4.332454158701391</v>
       </c>
       <c r="P22" t="n">
-        <v>335.8602619339183</v>
+        <v>335.8608948148934</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36871,7 +36956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W407"/>
+  <dimension ref="A1:W408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84457,6 +84542,123 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:53:39+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-38.274477263076015,178.33038186002491</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>-38.275164474525724,178.3306161734529</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-38.275840717506625,178.33088360106055</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-38.276514379287484,178.33115880747417</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-38.27718246960918,178.3314459824673</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-38.27781499907188,178.33183493399346</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-38.27846481325496,178.33217573387924</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>-38.27911349685082,178.33252721931385</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-38.279767964066636,178.3328722927005</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>-38.28041399191862,178.3332488975262</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>-38.28104120459702,178.33366845779884</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>-38.28165013019914,178.33412751553004</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>-38.28224503373493,178.33461832896097</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>-38.28280476704312,178.3351645102</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>-38.28333816655372,178.3357478094242</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>-38.283850811820365,178.3363658246272</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>-38.284366267652395,178.33698689088493</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>-38.28489333612337,178.33758493400708</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>-38.28537750712551,178.33824609927464</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>-38.28580921468723,178.3389720305516</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>-38.286176810090694,178.3397505437201</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0253/nzd0253.xlsx
+++ b/data/nzd0253/nzd0253.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W408"/>
+  <dimension ref="A1:W410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31052,6 +31052,156 @@
       <c r="W408" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>340.73</v>
+      </c>
+      <c r="C409" t="n">
+        <v>331.73</v>
+      </c>
+      <c r="D409" t="n">
+        <v>327.27</v>
+      </c>
+      <c r="E409" t="n">
+        <v>324.56</v>
+      </c>
+      <c r="F409" t="n">
+        <v>321.89</v>
+      </c>
+      <c r="G409" t="n">
+        <v>329.76</v>
+      </c>
+      <c r="H409" t="n">
+        <v>333.16</v>
+      </c>
+      <c r="I409" t="n">
+        <v>337.99</v>
+      </c>
+      <c r="J409" t="n">
+        <v>342.51</v>
+      </c>
+      <c r="K409" t="n">
+        <v>346.34</v>
+      </c>
+      <c r="L409" t="n">
+        <v>347.79</v>
+      </c>
+      <c r="M409" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="N409" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="O409" t="n">
+        <v>353.37</v>
+      </c>
+      <c r="P409" t="n">
+        <v>360.4</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>355.46</v>
+      </c>
+      <c r="R409" t="n">
+        <v>346.98</v>
+      </c>
+      <c r="S409" t="n">
+        <v>340.01</v>
+      </c>
+      <c r="T409" t="n">
+        <v>342.33</v>
+      </c>
+      <c r="U409" t="n">
+        <v>345.08</v>
+      </c>
+      <c r="V409" t="n">
+        <v>344.76</v>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>342.49</v>
+      </c>
+      <c r="C410" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="D410" t="n">
+        <v>327.92</v>
+      </c>
+      <c r="E410" t="n">
+        <v>326.58</v>
+      </c>
+      <c r="F410" t="n">
+        <v>324.08</v>
+      </c>
+      <c r="G410" t="n">
+        <v>330.03</v>
+      </c>
+      <c r="H410" t="n">
+        <v>333.21</v>
+      </c>
+      <c r="I410" t="n">
+        <v>337.37</v>
+      </c>
+      <c r="J410" t="n">
+        <v>341.7</v>
+      </c>
+      <c r="K410" t="n">
+        <v>346.18</v>
+      </c>
+      <c r="L410" t="n">
+        <v>346.83</v>
+      </c>
+      <c r="M410" t="n">
+        <v>352.31</v>
+      </c>
+      <c r="N410" t="n">
+        <v>349.54</v>
+      </c>
+      <c r="O410" t="n">
+        <v>352.61</v>
+      </c>
+      <c r="P410" t="n">
+        <v>361.38</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>357.62</v>
+      </c>
+      <c r="R410" t="n">
+        <v>349.16</v>
+      </c>
+      <c r="S410" t="n">
+        <v>341.84</v>
+      </c>
+      <c r="T410" t="n">
+        <v>343.56</v>
+      </c>
+      <c r="U410" t="n">
+        <v>346.96</v>
+      </c>
+      <c r="V410" t="n">
+        <v>346.88</v>
+      </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31066,7 +31216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35169,6 +35319,26 @@
       </c>
       <c r="B410" t="n">
         <v>-0.62</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>-0.26</v>
       </c>
     </row>
   </sheetData>
@@ -35337,28 +35507,28 @@
         <v>0.0723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1992396335194262</v>
+        <v>0.1950650917567181</v>
       </c>
       <c r="J2" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K2" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1254861221436964</v>
+        <v>0.1216626553589991</v>
       </c>
       <c r="M2" t="n">
-        <v>3.154159126718568</v>
+        <v>3.157034033205021</v>
       </c>
       <c r="N2" t="n">
-        <v>15.26156072975101</v>
+        <v>15.26845479149437</v>
       </c>
       <c r="O2" t="n">
-        <v>3.906604757298979</v>
+        <v>3.907487017444124</v>
       </c>
       <c r="P2" t="n">
-        <v>340.3213863314922</v>
+        <v>340.3637516438558</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35415,28 +35585,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2370297685539546</v>
+        <v>0.2324494941464132</v>
       </c>
       <c r="J3" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K3" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1463570019917254</v>
+        <v>0.1424270406153972</v>
       </c>
       <c r="M3" t="n">
-        <v>3.425393670584879</v>
+        <v>3.428103689462136</v>
       </c>
       <c r="N3" t="n">
-        <v>18.0777774731358</v>
+        <v>18.08288650227519</v>
       </c>
       <c r="O3" t="n">
-        <v>4.251796969886474</v>
+        <v>4.252397735663398</v>
       </c>
       <c r="P3" t="n">
-        <v>329.9035783568534</v>
+        <v>329.9500813819456</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35493,28 +35663,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2492867630387995</v>
+        <v>0.243149658758587</v>
       </c>
       <c r="J4" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K4" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1528002575130897</v>
+        <v>0.1469002538191048</v>
       </c>
       <c r="M4" t="n">
-        <v>3.463975939307727</v>
+        <v>3.481327775768285</v>
       </c>
       <c r="N4" t="n">
-        <v>19.00800945318594</v>
+        <v>19.08343337073434</v>
       </c>
       <c r="O4" t="n">
-        <v>4.359817594026835</v>
+        <v>4.368458924006765</v>
       </c>
       <c r="P4" t="n">
-        <v>326.8553245405971</v>
+        <v>326.9176289059172</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35571,28 +35741,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1915603833873838</v>
+        <v>0.1864252794211725</v>
       </c>
       <c r="J5" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K5" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07807146444517543</v>
+        <v>0.07474886997833607</v>
       </c>
       <c r="M5" t="n">
-        <v>3.864346350122593</v>
+        <v>3.871113448565658</v>
       </c>
       <c r="N5" t="n">
-        <v>23.90522305621634</v>
+        <v>23.91093261555576</v>
       </c>
       <c r="O5" t="n">
-        <v>4.889296785450474</v>
+        <v>4.889880634080525</v>
       </c>
       <c r="P5" t="n">
-        <v>325.4114582084385</v>
+        <v>325.4635734231057</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35649,28 +35819,28 @@
         <v>0.0835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1979249810866058</v>
+        <v>0.19235337618939</v>
       </c>
       <c r="J6" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K6" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0815723874416342</v>
+        <v>0.07785708432117544</v>
       </c>
       <c r="M6" t="n">
-        <v>4.053220601234132</v>
+        <v>4.062089297682239</v>
       </c>
       <c r="N6" t="n">
-        <v>24.33209239068246</v>
+        <v>24.35744008075371</v>
       </c>
       <c r="O6" t="n">
-        <v>4.932757078012505</v>
+        <v>4.935325731980992</v>
       </c>
       <c r="P6" t="n">
-        <v>323.0757402929611</v>
+        <v>323.1322854830011</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35727,28 +35897,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2247803053162964</v>
+        <v>0.2256747108874452</v>
       </c>
       <c r="J7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08632253806420742</v>
+        <v>0.08793041297873105</v>
       </c>
       <c r="M7" t="n">
-        <v>4.498561194980025</v>
+        <v>4.479888185509314</v>
       </c>
       <c r="N7" t="n">
-        <v>29.50269559154901</v>
+        <v>29.36206316260775</v>
       </c>
       <c r="O7" t="n">
-        <v>5.431638389247669</v>
+        <v>5.418677252116771</v>
       </c>
       <c r="P7" t="n">
-        <v>323.0369363360891</v>
+        <v>323.0278524078043</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35805,28 +35975,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.149506612220869</v>
+        <v>0.15248154760427</v>
       </c>
       <c r="J8" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K8" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04575599526163565</v>
+        <v>0.04800144441402288</v>
       </c>
       <c r="M8" t="n">
-        <v>4.037462676236879</v>
+        <v>4.028584124347777</v>
       </c>
       <c r="N8" t="n">
-        <v>25.71631332638964</v>
+        <v>25.62999275266995</v>
       </c>
       <c r="O8" t="n">
-        <v>5.07112544967975</v>
+        <v>5.062607307768395</v>
       </c>
       <c r="P8" t="n">
-        <v>326.3346902601034</v>
+        <v>326.3044846872731</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35883,28 +36053,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2100574322950579</v>
+        <v>0.215254296947991</v>
       </c>
       <c r="J9" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K9" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1071329139232431</v>
+        <v>0.1125392146236089</v>
       </c>
       <c r="M9" t="n">
-        <v>3.452943837122695</v>
+        <v>3.454539783732269</v>
       </c>
       <c r="N9" t="n">
-        <v>20.28693673104069</v>
+        <v>20.30864128626788</v>
       </c>
       <c r="O9" t="n">
-        <v>4.50410221143356</v>
+        <v>4.506510988144584</v>
       </c>
       <c r="P9" t="n">
-        <v>327.0757539036312</v>
+        <v>327.0229962022433</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35961,28 +36131,28 @@
         <v>0.0864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1970533267253037</v>
+        <v>0.203144651927379</v>
       </c>
       <c r="J10" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K10" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05717428229327537</v>
+        <v>0.06098459037763493</v>
       </c>
       <c r="M10" t="n">
-        <v>4.528294562095632</v>
+        <v>4.523397651216309</v>
       </c>
       <c r="N10" t="n">
-        <v>35.3243935592741</v>
+        <v>35.31793577844693</v>
       </c>
       <c r="O10" t="n">
-        <v>5.943432809351352</v>
+        <v>5.942889514238585</v>
       </c>
       <c r="P10" t="n">
-        <v>330.9858663656184</v>
+        <v>330.9240291747893</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36039,28 +36209,28 @@
         <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1317274978911523</v>
+        <v>0.138295111854685</v>
       </c>
       <c r="J11" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K11" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01905193660791815</v>
+        <v>0.02113308645053102</v>
       </c>
       <c r="M11" t="n">
-        <v>5.501844647655032</v>
+        <v>5.497872316899389</v>
       </c>
       <c r="N11" t="n">
-        <v>49.28743816903048</v>
+        <v>49.23866812198703</v>
       </c>
       <c r="O11" t="n">
-        <v>7.020501276193209</v>
+        <v>7.017027014483201</v>
       </c>
       <c r="P11" t="n">
-        <v>336.4233285431909</v>
+        <v>336.3566480103183</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36117,28 +36287,28 @@
         <v>0.1196</v>
       </c>
       <c r="I12" t="n">
-        <v>0.138983190504317</v>
+        <v>0.1446267593262984</v>
       </c>
       <c r="J12" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K12" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02340584644160637</v>
+        <v>0.02552322908803339</v>
       </c>
       <c r="M12" t="n">
-        <v>5.296592406051601</v>
+        <v>5.287253951153291</v>
       </c>
       <c r="N12" t="n">
-        <v>44.46218449977638</v>
+        <v>44.38795121692471</v>
       </c>
       <c r="O12" t="n">
-        <v>6.667997038074956</v>
+        <v>6.662428327338667</v>
       </c>
       <c r="P12" t="n">
-        <v>338.1685271248453</v>
+        <v>338.1112376998045</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36195,28 +36365,28 @@
         <v>0.0833</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1642375658850476</v>
+        <v>0.1687877248008474</v>
       </c>
       <c r="J13" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K13" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03634688022317789</v>
+        <v>0.03868091407841412</v>
       </c>
       <c r="M13" t="n">
-        <v>4.933260047043349</v>
+        <v>4.923669721771118</v>
       </c>
       <c r="N13" t="n">
-        <v>39.54318176058321</v>
+        <v>39.44321723695442</v>
       </c>
       <c r="O13" t="n">
-        <v>6.288336963027921</v>
+        <v>6.2803835262629</v>
       </c>
       <c r="P13" t="n">
-        <v>344.0433811219953</v>
+        <v>343.9972293386555</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36273,28 +36443,28 @@
         <v>0.0706</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07167929591305294</v>
+        <v>0.07472829361736257</v>
       </c>
       <c r="J14" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K14" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007631850900525983</v>
+        <v>0.008382234520140308</v>
       </c>
       <c r="M14" t="n">
-        <v>4.821365548866417</v>
+        <v>4.806512618637382</v>
       </c>
       <c r="N14" t="n">
-        <v>36.94055536464012</v>
+        <v>36.80225238035724</v>
       </c>
       <c r="O14" t="n">
-        <v>6.077874247188742</v>
+        <v>6.066485999353929</v>
       </c>
       <c r="P14" t="n">
-        <v>345.17489945391</v>
+        <v>345.1439771921729</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36351,28 +36521,28 @@
         <v>0.1594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06272925841530448</v>
+        <v>0.06424342668264159</v>
       </c>
       <c r="J15" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K15" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007081115209472633</v>
+        <v>0.007513686211713444</v>
       </c>
       <c r="M15" t="n">
-        <v>4.329814967955969</v>
+        <v>4.314960558105975</v>
       </c>
       <c r="N15" t="n">
-        <v>30.5088218147959</v>
+        <v>30.37026945006161</v>
       </c>
       <c r="O15" t="n">
-        <v>5.523479140432767</v>
+        <v>5.510922740345904</v>
       </c>
       <c r="P15" t="n">
-        <v>349.8580193355851</v>
+        <v>349.8426662309168</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36429,28 +36599,28 @@
         <v>0.1171</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.02215306994081502</v>
+        <v>-0.02136593780762742</v>
       </c>
       <c r="J16" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K16" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001169905482966249</v>
+        <v>0.001101708311431082</v>
       </c>
       <c r="M16" t="n">
-        <v>3.886799406968577</v>
+        <v>3.871200107115368</v>
       </c>
       <c r="N16" t="n">
-        <v>23.11453460163344</v>
+        <v>23.0054367146284</v>
       </c>
       <c r="O16" t="n">
-        <v>4.807757751970605</v>
+        <v>4.796398306503371</v>
       </c>
       <c r="P16" t="n">
-        <v>360.7234890566173</v>
+        <v>360.7154859418314</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36507,28 +36677,28 @@
         <v>0.0732</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.01461587700598413</v>
+        <v>-0.01168801165022177</v>
       </c>
       <c r="J17" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K17" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0004577379174542928</v>
+        <v>0.0002959115983715011</v>
       </c>
       <c r="M17" t="n">
-        <v>4.195863360144211</v>
+        <v>4.187903618749599</v>
       </c>
       <c r="N17" t="n">
-        <v>25.73419011883626</v>
+        <v>25.65208495460192</v>
       </c>
       <c r="O17" t="n">
-        <v>5.072887749481183</v>
+        <v>5.064788737410665</v>
       </c>
       <c r="P17" t="n">
-        <v>354.115700930137</v>
+        <v>354.0859491940304</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36585,28 +36755,28 @@
         <v>0.1014</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03933570135990321</v>
+        <v>0.04245455041166162</v>
       </c>
       <c r="J18" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K18" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005659668965879772</v>
+        <v>0.006646538444608163</v>
       </c>
       <c r="M18" t="n">
-        <v>3.254873242252718</v>
+        <v>3.25473288913185</v>
       </c>
       <c r="N18" t="n">
-        <v>14.99665134610542</v>
+        <v>14.97230612539956</v>
       </c>
       <c r="O18" t="n">
-        <v>3.872551012718285</v>
+        <v>3.86940643062984</v>
       </c>
       <c r="P18" t="n">
-        <v>344.0223249138597</v>
+        <v>343.9906338215837</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36663,28 +36833,28 @@
         <v>0.1035</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0558066518047014</v>
+        <v>0.05999067872528649</v>
       </c>
       <c r="J19" t="n">
+        <v>409</v>
+      </c>
+      <c r="K19" t="n">
         <v>407</v>
       </c>
-      <c r="K19" t="n">
-        <v>405</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01181192915424123</v>
+        <v>0.01371432345062906</v>
       </c>
       <c r="M19" t="n">
-        <v>3.126071567033773</v>
+        <v>3.130329715157822</v>
       </c>
       <c r="N19" t="n">
-        <v>14.43995309025057</v>
+        <v>14.4513709952756</v>
       </c>
       <c r="O19" t="n">
-        <v>3.799993827659536</v>
+        <v>3.801495889156741</v>
       </c>
       <c r="P19" t="n">
-        <v>335.4072718045437</v>
+        <v>335.364835529114</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36741,28 +36911,28 @@
         <v>0.1228</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1619981713170918</v>
+        <v>0.1663657348048793</v>
       </c>
       <c r="J20" t="n">
+        <v>409</v>
+      </c>
+      <c r="K20" t="n">
         <v>407</v>
       </c>
-      <c r="K20" t="n">
-        <v>405</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.09136747703393699</v>
+        <v>0.09643314476755704</v>
       </c>
       <c r="M20" t="n">
-        <v>3.107543970850342</v>
+        <v>3.113922491130955</v>
       </c>
       <c r="N20" t="n">
-        <v>14.46411758319737</v>
+        <v>14.48021093716003</v>
       </c>
       <c r="O20" t="n">
-        <v>3.803172042282254</v>
+        <v>3.805287234514633</v>
       </c>
       <c r="P20" t="n">
-        <v>334.4222707696968</v>
+        <v>334.3779809108851</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36819,28 +36989,28 @@
         <v>0.1003</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3503142482441595</v>
+        <v>0.3557411474266254</v>
       </c>
       <c r="J21" t="n">
+        <v>409</v>
+      </c>
+      <c r="K21" t="n">
         <v>407</v>
       </c>
-      <c r="K21" t="n">
-        <v>405</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.3028546588990126</v>
+        <v>0.3101748252141097</v>
       </c>
       <c r="M21" t="n">
-        <v>3.218991726645391</v>
+        <v>3.229019966173408</v>
       </c>
       <c r="N21" t="n">
-        <v>15.65596163007208</v>
+        <v>15.71498091254272</v>
       </c>
       <c r="O21" t="n">
-        <v>3.956761507858678</v>
+        <v>3.964212521112197</v>
       </c>
       <c r="P21" t="n">
-        <v>331.4531992552916</v>
+        <v>331.3981631517015</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36897,28 +37067,28 @@
         <v>0.1131</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2960503428328508</v>
+        <v>0.2981994768847513</v>
       </c>
       <c r="J22" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K22" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2048322800827984</v>
+        <v>0.2090142847246579</v>
       </c>
       <c r="M22" t="n">
-        <v>3.563721096177161</v>
+        <v>3.555687279054424</v>
       </c>
       <c r="N22" t="n">
-        <v>18.77015903724898</v>
+        <v>18.70416583107582</v>
       </c>
       <c r="O22" t="n">
-        <v>4.332454158701391</v>
+        <v>4.324831306661084</v>
       </c>
       <c r="P22" t="n">
-        <v>335.8608948148934</v>
+        <v>335.839050520375</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36956,7 +37126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W408"/>
+  <dimension ref="A1:W410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84659,6 +84829,240 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>-38.27447534895874,178.33038764199856</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>-38.27516663226761,178.3306096555368</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>-38.27584210960576,178.3308793959196</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-38.2765114906651,178.33116753321053</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>-38.277179371240784,178.33145546212398</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>-38.27781149284742,178.33184604977535</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-38.278464420445054,178.33217700823047</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>-38.27911451161801,178.3325239272158</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>-38.279769119705804,178.33286882710686</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>-38.28041258297535,178.33325246591355</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>-38.281040427554856,178.3336702581211</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>-38.28164998375004,178.33412780277354</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>-38.282245471551306,178.33461760529303</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>-38.28280206019075,178.3351689179464</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>-38.28333373856306,178.33575363974504</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>-38.28383923681378,178.33637794940958</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>-38.2843617273298,178.33699173486139</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>-38.284888457609725,178.33759050088943</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>-38.28537549890654,178.3382482075915</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>-38.28580079326069,178.33897881798651</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>-38.28616773134227,178.339756813403</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>-38.27446922378168,178.33040614431195</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>-38.27516604062873,178.33061144270738</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>-38.2758398474446,178.33088622927355</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-38.27650446052137,178.33118876933685</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-38.27717183187469,178.33147852928485</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>-38.27781059124668,178.33184890811904</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>-38.27846425677425,178.33217753921016</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>-38.27911654115218,178.33251734301933</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>-38.279771956274224,178.33286032064933</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>-38.28041322706372,178.33325083465078</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>-38.281044571779454,178.33366065640203</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>-38.28165486538604,178.33411822798985</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>-38.282250780074385,178.33460883081847</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>-38.28280625857397,178.33516208144164</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>-38.28332762668822,178.33576168722897</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>-38.28382426554633,178.3363936317572</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>-38.284346730505604,178.3370077346581</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>-38.28487622791015,178.33760445622136</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>-38.28536698128786,178.33825714976174</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>-38.28578652994302,178.33899031381875</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>-38.28615099486628,178.33976837142325</t>
+        </is>
+      </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0253/nzd0253.xlsx
+++ b/data/nzd0253/nzd0253.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W410"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31200,6 +31200,306 @@
         <v>346.88</v>
       </c>
       <c r="W410" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:04+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>342.14</v>
+      </c>
+      <c r="C411" t="n">
+        <v>332.92</v>
+      </c>
+      <c r="D411" t="n">
+        <v>328.96</v>
+      </c>
+      <c r="E411" t="n">
+        <v>327.35</v>
+      </c>
+      <c r="F411" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="G411" t="n">
+        <v>329.17</v>
+      </c>
+      <c r="H411" t="n">
+        <v>332.34</v>
+      </c>
+      <c r="I411" t="n">
+        <v>336.99</v>
+      </c>
+      <c r="J411" t="n">
+        <v>340.71</v>
+      </c>
+      <c r="K411" t="n">
+        <v>345.15</v>
+      </c>
+      <c r="L411" t="n">
+        <v>345.65</v>
+      </c>
+      <c r="M411" t="n">
+        <v>351.71</v>
+      </c>
+      <c r="N411" t="n">
+        <v>349.08</v>
+      </c>
+      <c r="O411" t="n">
+        <v>351.82</v>
+      </c>
+      <c r="P411" t="n">
+        <v>361.49</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>357.01</v>
+      </c>
+      <c r="R411" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="S411" t="n">
+        <v>341.82</v>
+      </c>
+      <c r="T411" t="n">
+        <v>343.92</v>
+      </c>
+      <c r="U411" t="n">
+        <v>346.85</v>
+      </c>
+      <c r="V411" t="n">
+        <v>347.02</v>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:11+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>340.66</v>
+      </c>
+      <c r="C412" t="n">
+        <v>331.95</v>
+      </c>
+      <c r="D412" t="n">
+        <v>328.92</v>
+      </c>
+      <c r="E412" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="F412" t="n">
+        <v>323.55</v>
+      </c>
+      <c r="G412" t="n">
+        <v>327.65</v>
+      </c>
+      <c r="H412" t="n">
+        <v>330.09</v>
+      </c>
+      <c r="I412" t="n">
+        <v>335.94</v>
+      </c>
+      <c r="J412" t="n">
+        <v>339.34</v>
+      </c>
+      <c r="K412" t="n">
+        <v>343.7</v>
+      </c>
+      <c r="L412" t="n">
+        <v>343.57</v>
+      </c>
+      <c r="M412" t="n">
+        <v>349.72</v>
+      </c>
+      <c r="N412" t="n">
+        <v>347.32</v>
+      </c>
+      <c r="O412" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="P412" t="n">
+        <v>360.4</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>355.94</v>
+      </c>
+      <c r="R412" t="n">
+        <v>348.1</v>
+      </c>
+      <c r="S412" t="n">
+        <v>341.81</v>
+      </c>
+      <c r="T412" t="n">
+        <v>343.67</v>
+      </c>
+      <c r="U412" t="n">
+        <v>345.98</v>
+      </c>
+      <c r="V412" t="n">
+        <v>346.88</v>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:52:47+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>341.61</v>
+      </c>
+      <c r="C413" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="D413" t="n">
+        <v>330.81</v>
+      </c>
+      <c r="E413" t="n">
+        <v>328.33</v>
+      </c>
+      <c r="F413" t="n">
+        <v>324.81</v>
+      </c>
+      <c r="G413" t="n">
+        <v>327.98</v>
+      </c>
+      <c r="H413" t="n">
+        <v>329.44</v>
+      </c>
+      <c r="I413" t="n">
+        <v>335.72</v>
+      </c>
+      <c r="J413" t="n">
+        <v>339.21</v>
+      </c>
+      <c r="K413" t="n">
+        <v>342.77</v>
+      </c>
+      <c r="L413" t="n">
+        <v>343.13</v>
+      </c>
+      <c r="M413" t="n">
+        <v>349.48</v>
+      </c>
+      <c r="N413" t="n">
+        <v>347.73</v>
+      </c>
+      <c r="O413" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="P413" t="n">
+        <v>361.35</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>356.79</v>
+      </c>
+      <c r="R413" t="n">
+        <v>348.73</v>
+      </c>
+      <c r="S413" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="T413" t="n">
+        <v>344.55</v>
+      </c>
+      <c r="U413" t="n">
+        <v>346.96</v>
+      </c>
+      <c r="V413" t="n">
+        <v>348.63</v>
+      </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>342.85</v>
+      </c>
+      <c r="C414" t="n">
+        <v>332.71</v>
+      </c>
+      <c r="D414" t="n">
+        <v>331.09</v>
+      </c>
+      <c r="E414" t="n">
+        <v>328.21</v>
+      </c>
+      <c r="F414" t="n">
+        <v>324.39</v>
+      </c>
+      <c r="G414" t="n">
+        <v>327.61</v>
+      </c>
+      <c r="H414" t="n">
+        <v>328.3</v>
+      </c>
+      <c r="I414" t="n">
+        <v>335.53</v>
+      </c>
+      <c r="J414" t="n">
+        <v>338.9</v>
+      </c>
+      <c r="K414" t="n">
+        <v>342.25</v>
+      </c>
+      <c r="L414" t="n">
+        <v>342.95</v>
+      </c>
+      <c r="M414" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="N414" t="n">
+        <v>347.34</v>
+      </c>
+      <c r="O414" t="n">
+        <v>350.31</v>
+      </c>
+      <c r="P414" t="n">
+        <v>361.11</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>356.27</v>
+      </c>
+      <c r="R414" t="n">
+        <v>348.71</v>
+      </c>
+      <c r="S414" t="n">
+        <v>343.58</v>
+      </c>
+      <c r="T414" t="n">
+        <v>344.65</v>
+      </c>
+      <c r="U414" t="n">
+        <v>346.54</v>
+      </c>
+      <c r="V414" t="n">
+        <v>348.83</v>
+      </c>
+      <c r="W414" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31216,7 +31516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B412"/>
+  <dimension ref="A1:B416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35339,6 +35639,46 @@
       </c>
       <c r="B412" t="n">
         <v>-0.26</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -35507,28 +35847,28 @@
         <v>0.0723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1950650917567181</v>
+        <v>0.1874231072703077</v>
       </c>
       <c r="J2" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K2" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1216626553589991</v>
+        <v>0.114919614311825</v>
       </c>
       <c r="M2" t="n">
-        <v>3.157034033205021</v>
+        <v>3.160184974932364</v>
       </c>
       <c r="N2" t="n">
-        <v>15.26845479149437</v>
+        <v>15.25992508864725</v>
       </c>
       <c r="O2" t="n">
-        <v>3.907487017444124</v>
+        <v>3.906395408640457</v>
       </c>
       <c r="P2" t="n">
-        <v>340.3637516438558</v>
+        <v>340.4416663758296</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35585,28 +35925,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2324494941464132</v>
+        <v>0.2252304129644437</v>
       </c>
       <c r="J3" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K3" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1424270406153972</v>
+        <v>0.1369764406576517</v>
       </c>
       <c r="M3" t="n">
-        <v>3.428103689462136</v>
+        <v>3.425389659146032</v>
       </c>
       <c r="N3" t="n">
-        <v>18.08288650227519</v>
+        <v>18.02803607446809</v>
       </c>
       <c r="O3" t="n">
-        <v>4.252397735663398</v>
+        <v>4.245943484605993</v>
       </c>
       <c r="P3" t="n">
-        <v>329.9500813819456</v>
+        <v>330.0236902863638</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35663,28 +36003,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.243149658758587</v>
+        <v>0.2360950442915466</v>
       </c>
       <c r="J4" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K4" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1469002538191048</v>
+        <v>0.1418414685697735</v>
       </c>
       <c r="M4" t="n">
-        <v>3.481327775768285</v>
+        <v>3.486954103689703</v>
       </c>
       <c r="N4" t="n">
-        <v>19.08343337073434</v>
+        <v>19.02197581664304</v>
       </c>
       <c r="O4" t="n">
-        <v>4.368458924006765</v>
+        <v>4.361419014110321</v>
       </c>
       <c r="P4" t="n">
-        <v>326.9176289059172</v>
+        <v>326.9895428545925</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35741,28 +36081,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1864252794211725</v>
+        <v>0.1808303662714887</v>
       </c>
       <c r="J5" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K5" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07474886997833607</v>
+        <v>0.07205151413308508</v>
       </c>
       <c r="M5" t="n">
-        <v>3.871113448565658</v>
+        <v>3.861495578528962</v>
       </c>
       <c r="N5" t="n">
-        <v>23.91093261555576</v>
+        <v>23.75423546659752</v>
       </c>
       <c r="O5" t="n">
-        <v>4.889880634080525</v>
+        <v>4.873831702736311</v>
       </c>
       <c r="P5" t="n">
-        <v>325.4635734231057</v>
+        <v>325.5206130633441</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35819,28 +36159,28 @@
         <v>0.0835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.19235337618939</v>
+        <v>0.1843686474042426</v>
       </c>
       <c r="J6" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K6" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07785708432117544</v>
+        <v>0.0732175150384613</v>
       </c>
       <c r="M6" t="n">
-        <v>4.062089297682239</v>
+        <v>4.063159934701138</v>
       </c>
       <c r="N6" t="n">
-        <v>24.35744008075371</v>
+        <v>24.26914906150447</v>
       </c>
       <c r="O6" t="n">
-        <v>4.935325731980992</v>
+        <v>4.926372809837322</v>
       </c>
       <c r="P6" t="n">
-        <v>323.1322854830011</v>
+        <v>323.2137005896292</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35897,28 +36237,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2256747108874452</v>
+        <v>0.2237127145356853</v>
       </c>
       <c r="J7" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K7" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08793041297873105</v>
+        <v>0.08845599925980263</v>
       </c>
       <c r="M7" t="n">
-        <v>4.479888185509314</v>
+        <v>4.448170897883082</v>
       </c>
       <c r="N7" t="n">
-        <v>29.36206316260775</v>
+        <v>29.09037079120081</v>
       </c>
       <c r="O7" t="n">
-        <v>5.418677252116771</v>
+        <v>5.393548997756562</v>
       </c>
       <c r="P7" t="n">
-        <v>323.0278524078043</v>
+        <v>323.0478678263019</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35975,28 +36315,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.15248154760427</v>
+        <v>0.1517705963963761</v>
       </c>
       <c r="J8" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K8" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04800144441402288</v>
+        <v>0.04865508589305656</v>
       </c>
       <c r="M8" t="n">
-        <v>4.028584124347777</v>
+        <v>4.00308428107034</v>
       </c>
       <c r="N8" t="n">
-        <v>25.62999275266995</v>
+        <v>25.40402995719878</v>
       </c>
       <c r="O8" t="n">
-        <v>5.062607307768395</v>
+        <v>5.040241061417477</v>
       </c>
       <c r="P8" t="n">
-        <v>326.3044846872731</v>
+        <v>326.3117626963121</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36053,28 +36393,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.215254296947991</v>
+        <v>0.22185436496137</v>
       </c>
       <c r="J9" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K9" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1125392146236089</v>
+        <v>0.1207538460190354</v>
       </c>
       <c r="M9" t="n">
-        <v>3.454539783732269</v>
+        <v>3.445162300630147</v>
       </c>
       <c r="N9" t="n">
-        <v>20.30864128626788</v>
+        <v>20.21450162380053</v>
       </c>
       <c r="O9" t="n">
-        <v>4.506510988144584</v>
+        <v>4.496054005881216</v>
       </c>
       <c r="P9" t="n">
-        <v>327.0229962022433</v>
+        <v>326.9557090150703</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36131,28 +36471,28 @@
         <v>0.0864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.203144651927379</v>
+        <v>0.2095774293760318</v>
       </c>
       <c r="J10" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K10" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06098459037763493</v>
+        <v>0.06597328079394416</v>
       </c>
       <c r="M10" t="n">
-        <v>4.523397651216309</v>
+        <v>4.497738176838993</v>
       </c>
       <c r="N10" t="n">
-        <v>35.31793577844693</v>
+        <v>35.07501085281768</v>
       </c>
       <c r="O10" t="n">
-        <v>5.942889514238585</v>
+        <v>5.922415964183678</v>
       </c>
       <c r="P10" t="n">
-        <v>330.9240291747893</v>
+        <v>330.8584498657758</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36209,28 +36549,28 @@
         <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.138295111854685</v>
+        <v>0.1451923415270065</v>
       </c>
       <c r="J11" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K11" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02113308645053102</v>
+        <v>0.02374742765279825</v>
       </c>
       <c r="M11" t="n">
-        <v>5.497872316899389</v>
+        <v>5.468652355999121</v>
       </c>
       <c r="N11" t="n">
-        <v>49.23866812198703</v>
+        <v>48.88218540031747</v>
       </c>
       <c r="O11" t="n">
-        <v>7.017027014483201</v>
+        <v>6.991579606949882</v>
       </c>
       <c r="P11" t="n">
-        <v>336.3566480103183</v>
+        <v>336.2863420362092</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36287,28 +36627,28 @@
         <v>0.1196</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1446267593262984</v>
+        <v>0.1483523798253973</v>
       </c>
       <c r="J12" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K12" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02552322908803339</v>
+        <v>0.02743850837684503</v>
       </c>
       <c r="M12" t="n">
-        <v>5.287253951153291</v>
+        <v>5.246843861416212</v>
       </c>
       <c r="N12" t="n">
-        <v>44.38795121692471</v>
+        <v>44.00106456645595</v>
       </c>
       <c r="O12" t="n">
-        <v>6.662428327338667</v>
+        <v>6.633329824941313</v>
       </c>
       <c r="P12" t="n">
-        <v>338.1112376998045</v>
+        <v>338.0732686407119</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36365,28 +36705,28 @@
         <v>0.0833</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1687877248008474</v>
+        <v>0.1720272096534362</v>
       </c>
       <c r="J13" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K13" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03868091407841412</v>
+        <v>0.04103817383575181</v>
       </c>
       <c r="M13" t="n">
-        <v>4.923669721771118</v>
+        <v>4.886076260003859</v>
       </c>
       <c r="N13" t="n">
-        <v>39.44321723695442</v>
+        <v>39.09270548766175</v>
       </c>
       <c r="O13" t="n">
-        <v>6.2803835262629</v>
+        <v>6.252415972059261</v>
       </c>
       <c r="P13" t="n">
-        <v>343.9972293386555</v>
+        <v>343.9642380077962</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36443,28 +36783,28 @@
         <v>0.0706</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07472829361736257</v>
+        <v>0.07618650152067215</v>
       </c>
       <c r="J14" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K14" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008382234520140308</v>
+        <v>0.008920668362261019</v>
       </c>
       <c r="M14" t="n">
-        <v>4.806512618637382</v>
+        <v>4.764012950794477</v>
       </c>
       <c r="N14" t="n">
-        <v>36.80225238035724</v>
+        <v>36.45484304750676</v>
       </c>
       <c r="O14" t="n">
-        <v>6.066485999353929</v>
+        <v>6.037784614203025</v>
       </c>
       <c r="P14" t="n">
-        <v>345.1439771921729</v>
+        <v>345.1291306346748</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36521,28 +36861,28 @@
         <v>0.1594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06424342668264159</v>
+        <v>0.06248248797281011</v>
       </c>
       <c r="J15" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K15" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007513686211713444</v>
+        <v>0.007282118391659487</v>
       </c>
       <c r="M15" t="n">
-        <v>4.314960558105975</v>
+        <v>4.283507554328716</v>
       </c>
       <c r="N15" t="n">
-        <v>30.37026945006161</v>
+        <v>30.08658413539496</v>
       </c>
       <c r="O15" t="n">
-        <v>5.510922740345904</v>
+        <v>5.485123894261183</v>
       </c>
       <c r="P15" t="n">
-        <v>349.8426662309168</v>
+        <v>349.8606184910201</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36599,28 +36939,28 @@
         <v>0.1171</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.02136593780762742</v>
+        <v>-0.01945118344137691</v>
       </c>
       <c r="J16" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K16" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001101708311431082</v>
+        <v>0.0009354214194117194</v>
       </c>
       <c r="M16" t="n">
-        <v>3.871200107115368</v>
+        <v>3.841860769211772</v>
       </c>
       <c r="N16" t="n">
-        <v>23.0054367146284</v>
+        <v>22.79270597227972</v>
       </c>
       <c r="O16" t="n">
-        <v>4.796398306503371</v>
+        <v>4.774170710424976</v>
       </c>
       <c r="P16" t="n">
-        <v>360.7154859418314</v>
+        <v>360.6959625588568</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36677,28 +37017,28 @@
         <v>0.0732</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.01168801165022177</v>
+        <v>-0.006156240961702731</v>
       </c>
       <c r="J17" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K17" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0002959115983715011</v>
+        <v>8.390644364075772e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.187903618749599</v>
+        <v>4.171282140851605</v>
       </c>
       <c r="N17" t="n">
-        <v>25.65208495460192</v>
+        <v>25.47516715860521</v>
       </c>
       <c r="O17" t="n">
-        <v>5.064788737410665</v>
+        <v>5.047293052578303</v>
       </c>
       <c r="P17" t="n">
-        <v>354.0859491940304</v>
+        <v>354.0295475626377</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36755,28 +37095,28 @@
         <v>0.1014</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04245455041166162</v>
+        <v>0.04948568191635502</v>
       </c>
       <c r="J18" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K18" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L18" t="n">
-        <v>0.006646538444608163</v>
+        <v>0.009160200400468832</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25473288913185</v>
+        <v>3.258167902001837</v>
       </c>
       <c r="N18" t="n">
-        <v>14.97230612539956</v>
+        <v>14.94084512325332</v>
       </c>
       <c r="O18" t="n">
-        <v>3.86940643062984</v>
+        <v>3.865338940281088</v>
       </c>
       <c r="P18" t="n">
-        <v>343.9906338215837</v>
+        <v>343.918940440631</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36833,28 +37173,28 @@
         <v>0.1035</v>
       </c>
       <c r="I19" t="n">
-        <v>0.05999067872528649</v>
+        <v>0.07142860339140468</v>
       </c>
       <c r="J19" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K19" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01371432345062906</v>
+        <v>0.01939300781135578</v>
       </c>
       <c r="M19" t="n">
-        <v>3.130329715157822</v>
+        <v>3.154157868498426</v>
       </c>
       <c r="N19" t="n">
-        <v>14.4513709952756</v>
+        <v>14.61700497431442</v>
       </c>
       <c r="O19" t="n">
-        <v>3.801495889156741</v>
+        <v>3.823219189938555</v>
       </c>
       <c r="P19" t="n">
-        <v>335.364835529114</v>
+        <v>335.2483705843794</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36911,28 +37251,28 @@
         <v>0.1228</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1663657348048793</v>
+        <v>0.1772343591672979</v>
       </c>
       <c r="J20" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K20" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09643314476755704</v>
+        <v>0.108577599399977</v>
       </c>
       <c r="M20" t="n">
-        <v>3.113922491130955</v>
+        <v>3.138112803084706</v>
       </c>
       <c r="N20" t="n">
-        <v>14.48021093716003</v>
+        <v>14.61178962249624</v>
       </c>
       <c r="O20" t="n">
-        <v>3.805287234514633</v>
+        <v>3.822537066203053</v>
       </c>
       <c r="P20" t="n">
-        <v>334.3779809108851</v>
+        <v>334.267320341547</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36989,28 +37329,28 @@
         <v>0.1003</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3557411474266254</v>
+        <v>0.3672039225263479</v>
       </c>
       <c r="J21" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K21" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3101748252141097</v>
+        <v>0.3250326953940539</v>
       </c>
       <c r="M21" t="n">
-        <v>3.229019966173408</v>
+        <v>3.252156575194928</v>
       </c>
       <c r="N21" t="n">
-        <v>15.71498091254272</v>
+        <v>15.86479901204355</v>
       </c>
       <c r="O21" t="n">
-        <v>3.964212521112197</v>
+        <v>3.983064023091211</v>
       </c>
       <c r="P21" t="n">
-        <v>331.3981631517015</v>
+        <v>331.2814604651799</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37067,28 +37407,28 @@
         <v>0.1131</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2981994768847513</v>
+        <v>0.306342658508033</v>
       </c>
       <c r="J22" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K22" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2090142847246579</v>
+        <v>0.2207862852543769</v>
       </c>
       <c r="M22" t="n">
-        <v>3.555687279054424</v>
+        <v>3.556678563463546</v>
       </c>
       <c r="N22" t="n">
-        <v>18.70416583107582</v>
+        <v>18.68172723225222</v>
       </c>
       <c r="O22" t="n">
-        <v>4.324831306661084</v>
+        <v>4.32223636931765</v>
       </c>
       <c r="P22" t="n">
-        <v>335.839050520375</v>
+        <v>335.7560025181114</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37126,7 +37466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W410"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85063,6 +85403,474 @@
         </is>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:04+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>-38.27447044185689,178.3304024648749</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>-38.27516249079498,178.3306221657303</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-38.27583622798596,178.33089716263888</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-38.276501780713176,178.33119686429472</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-38.277169972852285,178.33148421707713</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>-38.27781346301175,178.33183980376475</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-38.278467104645834,178.33216830016332</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-38.279117785060045,178.3325133075439</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-38.27977542319041,178.3328499238669</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>-38.28041737338204,178.33324033339593</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>-38.281049665721206,178.33364885428745</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>-38.28165779436728,178.334112483119</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>-38.28225329751813,178.33460466972696</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>-38.282810622682476,178.33515497507403</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>-38.28332694066142,178.33576259051787</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>-38.28382849354333,178.33638920294672</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>-38.28434886308161,178.33700545945806</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>-38.28487636156808,178.3376043037041</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>-38.285364488326195,178.3382597669819</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>-38.28578736449886,178.33898964119038</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>-38.28614988962727,178.33976913468857</t>
+        </is>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:11+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>-38.27447559257368,178.33038690611102</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>-38.27516586661731,178.3306119683458</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>-38.27583636719592,178.33089674212485</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-38.27650341644032,178.3311919232166</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-38.27717365647054,178.33147294682175</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-38.27781853868797,178.33182371234585</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-38.2784744698278,178.33214440607296</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-38.2791212221732,178.3325021568873</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-38.279780220840685,178.3328355363985</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-38.28042321043066,178.33322555007382</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>-38.281058644870164,178.33362805055577</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>-38.28166750881998,178.33409342929383</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>-38.2822629294756,178.33458874902635</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>-38.282818743237854,178.33514175183066</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>-38.28333373856306,178.33575363974504</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>-38.283835909865616,178.33638143437628</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>-38.284354022539596,178.33699995494126</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>-38.28487642839704,178.33760422744544</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>-38.28536621954957,178.3382579494679</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>-38.285793965076806,178.338984321311</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>-38.28615099486628,178.33976837142325</t>
+        </is>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:52:47+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-38.27447228637055,178.33039689315567</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>-38.27516269960876,178.33062153496428</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-38.275829789523534,178.33091661141083</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-38.276498370047435,178.3312071669674</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-38.27716931875174,178.33148621833732</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>-38.27781743673213,178.3318272058778</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-38.2784765975462,178.33213750333474</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-38.279121942330114,178.3324998205591</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-38.27978067609208,178.33283417116417</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-38.28042695419197,178.33321606835557</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-38.28106054430509,178.33362364976566</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>-38.28166868041207,178.33409113134468</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>-38.2822606856675,178.33459245782635</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-38.282819019447174,178.33514130206044</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>-38.283327813786435,178.33576144087743</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>-38.28383001839468,178.33638760567067</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>-38.2843496885949,178.33700457873542</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>-38.28486673819701,178.33761528494563</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>-38.285360125643166,178.33826434711676</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>-38.28578652994302,178.33899031381875</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>-38.28613717937844,178.33977791223808</t>
+        </is>
+      </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-38.27446797090423,178.33040992887564</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-38.27516322164319,178.3306199580492</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-38.27582881505329,178.33091955500842</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-38.27649878768001,178.33120590541571</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-38.277170764658166,178.33148179449898</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>-38.27781867225836,178.3318232888874</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-38.27848032923599,178.3321253969928</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-38.279122564283774,178.33249780282105</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-38.27978176169153,178.33283091560529</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-38.28042904747756,178.33321076674918</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-38.28106132134661,178.33362184944238</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>-38.28166833869771,178.33409180157986</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>-38.28226282002155,178.33458892994344</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-38.282818964205326,178.33514139201446</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>-38.28332931057214,178.33575947006517</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>-38.283833622588695,178.33638383029069</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>-38.28434982618045,178.33700443194832</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>-38.284864599669994,178.33761772522115</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>-38.285359433153786,178.33826507412226</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>-38.28578971642895,178.33898774560126</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>-38.286135600465514,178.3397790026167</t>
+        </is>
+      </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0253/nzd0253.xlsx
+++ b/data/nzd0253/nzd0253.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31500,6 +31500,81 @@
         <v>348.83</v>
       </c>
       <c r="W414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>342.51</v>
+      </c>
+      <c r="C415" t="n">
+        <v>332.62</v>
+      </c>
+      <c r="D415" t="n">
+        <v>331.02</v>
+      </c>
+      <c r="E415" t="n">
+        <v>328.31</v>
+      </c>
+      <c r="F415" t="n">
+        <v>324.57</v>
+      </c>
+      <c r="G415" t="n">
+        <v>327.16</v>
+      </c>
+      <c r="H415" t="n">
+        <v>327.52</v>
+      </c>
+      <c r="I415" t="n">
+        <v>335.72</v>
+      </c>
+      <c r="J415" t="n">
+        <v>339.61</v>
+      </c>
+      <c r="K415" t="n">
+        <v>341.47</v>
+      </c>
+      <c r="L415" t="n">
+        <v>343.32</v>
+      </c>
+      <c r="M415" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="N415" t="n">
+        <v>347.36</v>
+      </c>
+      <c r="O415" t="n">
+        <v>350.85</v>
+      </c>
+      <c r="P415" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>356.65</v>
+      </c>
+      <c r="R415" t="n">
+        <v>349.76</v>
+      </c>
+      <c r="S415" t="n">
+        <v>343.42</v>
+      </c>
+      <c r="T415" t="n">
+        <v>344.48</v>
+      </c>
+      <c r="U415" t="n">
+        <v>346.41</v>
+      </c>
+      <c r="V415" t="n">
+        <v>349.44</v>
+      </c>
+      <c r="W415" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31516,7 +31591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B416"/>
+  <dimension ref="A1:B417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35679,6 +35754,16 @@
       </c>
       <c r="B416" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>-0.76</v>
       </c>
     </row>
   </sheetData>
@@ -35847,28 +35932,28 @@
         <v>0.0723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1874231072703077</v>
+        <v>0.1859250585111105</v>
       </c>
       <c r="J2" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K2" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L2" t="n">
-        <v>0.114919614311825</v>
+        <v>0.1137642467464661</v>
       </c>
       <c r="M2" t="n">
-        <v>3.160184974932364</v>
+        <v>3.159296520294163</v>
       </c>
       <c r="N2" t="n">
-        <v>15.25992508864725</v>
+        <v>15.24409899526026</v>
       </c>
       <c r="O2" t="n">
-        <v>3.906395408640457</v>
+        <v>3.904369218613969</v>
       </c>
       <c r="P2" t="n">
-        <v>340.4416663758296</v>
+        <v>340.4569874675587</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35925,28 +36010,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2252304129644437</v>
+        <v>0.2234854854819171</v>
       </c>
       <c r="J3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1369764406576517</v>
+        <v>0.135667334212444</v>
       </c>
       <c r="M3" t="n">
-        <v>3.425389659146032</v>
+        <v>3.424735580999537</v>
       </c>
       <c r="N3" t="n">
-        <v>18.02803607446809</v>
+        <v>18.01302766938275</v>
       </c>
       <c r="O3" t="n">
-        <v>4.245943484605993</v>
+        <v>4.24417573497879</v>
       </c>
       <c r="P3" t="n">
-        <v>330.0236902863638</v>
+        <v>330.0415362969533</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36003,28 +36088,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2360950442915466</v>
+        <v>0.2349266092643272</v>
       </c>
       <c r="J4" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K4" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1418414685697735</v>
+        <v>0.1412854914852449</v>
       </c>
       <c r="M4" t="n">
-        <v>3.486954103689703</v>
+        <v>3.485068698530956</v>
       </c>
       <c r="N4" t="n">
-        <v>19.02197581664304</v>
+        <v>18.98882493312693</v>
       </c>
       <c r="O4" t="n">
-        <v>4.361419014110321</v>
+        <v>4.357616886915018</v>
       </c>
       <c r="P4" t="n">
-        <v>326.9895428545925</v>
+        <v>327.0014928663138</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36081,28 +36166,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1808303662714887</v>
+        <v>0.1797852488220567</v>
       </c>
       <c r="J5" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K5" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07205151413308508</v>
+        <v>0.07165118599638642</v>
       </c>
       <c r="M5" t="n">
-        <v>3.861495578528962</v>
+        <v>3.857386915361744</v>
       </c>
       <c r="N5" t="n">
-        <v>23.75423546659752</v>
+        <v>23.70709555312121</v>
       </c>
       <c r="O5" t="n">
-        <v>4.873831702736311</v>
+        <v>4.868993279223253</v>
       </c>
       <c r="P5" t="n">
-        <v>325.5206130633441</v>
+        <v>325.5313018611633</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36159,28 +36244,28 @@
         <v>0.0835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1843686474042426</v>
+        <v>0.1825535764604846</v>
       </c>
       <c r="J6" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K6" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0732175150384613</v>
+        <v>0.07220346953156875</v>
       </c>
       <c r="M6" t="n">
-        <v>4.063159934701138</v>
+        <v>4.062542167886436</v>
       </c>
       <c r="N6" t="n">
-        <v>24.26914906150447</v>
+        <v>24.24140595396806</v>
       </c>
       <c r="O6" t="n">
-        <v>4.926372809837322</v>
+        <v>4.923556230405829</v>
       </c>
       <c r="P6" t="n">
-        <v>323.2137005896292</v>
+        <v>323.2322639830123</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36237,28 +36322,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2237127145356853</v>
+        <v>0.2227556745537794</v>
       </c>
       <c r="J7" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K7" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08845599925980263</v>
+        <v>0.08822658939887029</v>
       </c>
       <c r="M7" t="n">
-        <v>4.448170897883082</v>
+        <v>4.442882046997982</v>
       </c>
       <c r="N7" t="n">
-        <v>29.09037079120081</v>
+        <v>29.02868884274492</v>
       </c>
       <c r="O7" t="n">
-        <v>5.393548997756562</v>
+        <v>5.387827840859888</v>
       </c>
       <c r="P7" t="n">
-        <v>323.0478678263019</v>
+        <v>323.0576558236959</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36315,28 +36400,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1517705963963761</v>
+        <v>0.15032318214129</v>
       </c>
       <c r="J8" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K8" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04865508589305656</v>
+        <v>0.04801487755850087</v>
       </c>
       <c r="M8" t="n">
-        <v>4.00308428107034</v>
+        <v>4.001658424909266</v>
       </c>
       <c r="N8" t="n">
-        <v>25.40402995719878</v>
+        <v>25.36230333900896</v>
       </c>
       <c r="O8" t="n">
-        <v>5.040241061417477</v>
+        <v>5.036100012808419</v>
       </c>
       <c r="P8" t="n">
-        <v>326.3117626963121</v>
+        <v>326.3265659304765</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36393,28 +36478,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.22185436496137</v>
+        <v>0.2232732866416096</v>
       </c>
       <c r="J9" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K9" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1207538460190354</v>
+        <v>0.1226604906480215</v>
       </c>
       <c r="M9" t="n">
-        <v>3.445162300630147</v>
+        <v>3.442071263324777</v>
       </c>
       <c r="N9" t="n">
-        <v>20.21450162380053</v>
+        <v>20.184544640676</v>
       </c>
       <c r="O9" t="n">
-        <v>4.496054005881216</v>
+        <v>4.492721295682161</v>
       </c>
       <c r="P9" t="n">
-        <v>326.9557090150703</v>
+        <v>326.9411971848739</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36471,28 +36556,28 @@
         <v>0.0864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2095774293760318</v>
+        <v>0.2111565644990347</v>
       </c>
       <c r="J10" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K10" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06597328079394416</v>
+        <v>0.06723946544609605</v>
       </c>
       <c r="M10" t="n">
-        <v>4.497738176838993</v>
+        <v>4.491278024802913</v>
       </c>
       <c r="N10" t="n">
-        <v>35.07501085281768</v>
+        <v>35.01366087457725</v>
       </c>
       <c r="O10" t="n">
-        <v>5.922415964183678</v>
+        <v>5.917234225090067</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8584498657758</v>
+        <v>330.8422994741923</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36549,28 +36634,28 @@
         <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1451923415270065</v>
+        <v>0.1458433623622382</v>
       </c>
       <c r="J11" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K11" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02374742765279825</v>
+        <v>0.0240950370027091</v>
       </c>
       <c r="M11" t="n">
-        <v>5.468652355999121</v>
+        <v>5.457717077135691</v>
       </c>
       <c r="N11" t="n">
-        <v>48.88218540031747</v>
+        <v>48.76808488062396</v>
       </c>
       <c r="O11" t="n">
-        <v>6.991579606949882</v>
+        <v>6.98341498699769</v>
       </c>
       <c r="P11" t="n">
-        <v>336.2863420362092</v>
+        <v>336.2796838083827</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36627,28 +36712,28 @@
         <v>0.1196</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1483523798253973</v>
+        <v>0.1489908726250141</v>
       </c>
       <c r="J12" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K12" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02743850837684503</v>
+        <v>0.02782875871437418</v>
       </c>
       <c r="M12" t="n">
-        <v>5.246843861416212</v>
+        <v>5.235997767061749</v>
       </c>
       <c r="N12" t="n">
-        <v>44.00106456645595</v>
+        <v>43.89860277789215</v>
       </c>
       <c r="O12" t="n">
-        <v>6.633329824941313</v>
+        <v>6.625602069087167</v>
       </c>
       <c r="P12" t="n">
-        <v>338.0732686407119</v>
+        <v>338.0667385416806</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36705,28 +36790,28 @@
         <v>0.0833</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1720272096534362</v>
+        <v>0.1727379686358515</v>
       </c>
       <c r="J13" t="n">
+        <v>414</v>
+      </c>
+      <c r="K13" t="n">
         <v>413</v>
       </c>
-      <c r="K13" t="n">
-        <v>412</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.04103817383575181</v>
+        <v>0.04159834938813389</v>
       </c>
       <c r="M13" t="n">
-        <v>4.886076260003859</v>
+        <v>4.876476996600418</v>
       </c>
       <c r="N13" t="n">
-        <v>39.09270548766175</v>
+        <v>39.00279863191609</v>
       </c>
       <c r="O13" t="n">
-        <v>6.252415972059261</v>
+        <v>6.245222064259693</v>
       </c>
       <c r="P13" t="n">
-        <v>343.9642380077962</v>
+        <v>343.9569742007046</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36783,28 +36868,28 @@
         <v>0.0706</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07618650152067215</v>
+        <v>0.07627850639985025</v>
       </c>
       <c r="J14" t="n">
+        <v>414</v>
+      </c>
+      <c r="K14" t="n">
         <v>413</v>
       </c>
-      <c r="K14" t="n">
-        <v>412</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.008920668362261019</v>
+        <v>0.00899550066465904</v>
       </c>
       <c r="M14" t="n">
-        <v>4.764012950794477</v>
+        <v>4.752736947655658</v>
       </c>
       <c r="N14" t="n">
-        <v>36.45484304750676</v>
+        <v>36.36665423125626</v>
       </c>
       <c r="O14" t="n">
-        <v>6.037784614203025</v>
+        <v>6.030477114727844</v>
       </c>
       <c r="P14" t="n">
-        <v>345.1291306346748</v>
+        <v>345.1281903641888</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36861,28 +36946,28 @@
         <v>0.1594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06248248797281011</v>
+        <v>0.06213555899742979</v>
       </c>
       <c r="J15" t="n">
+        <v>414</v>
+      </c>
+      <c r="K15" t="n">
         <v>413</v>
       </c>
-      <c r="K15" t="n">
-        <v>412</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.007282118391659487</v>
+        <v>0.007244940293750446</v>
       </c>
       <c r="M15" t="n">
-        <v>4.283507554328716</v>
+        <v>4.2749345033205</v>
       </c>
       <c r="N15" t="n">
-        <v>30.08658413539496</v>
+        <v>30.01486662783258</v>
       </c>
       <c r="O15" t="n">
-        <v>5.485123894261183</v>
+        <v>5.478582538196589</v>
       </c>
       <c r="P15" t="n">
-        <v>349.8606184910201</v>
+        <v>349.8641640320741</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36939,28 +37024,28 @@
         <v>0.1171</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01945118344137691</v>
+        <v>-0.01893032025023297</v>
       </c>
       <c r="J16" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K16" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0009354214194117194</v>
+        <v>0.0008912857050692446</v>
       </c>
       <c r="M16" t="n">
-        <v>3.841860769211772</v>
+        <v>3.834778048947695</v>
       </c>
       <c r="N16" t="n">
-        <v>22.79270597227972</v>
+        <v>22.74019391197051</v>
       </c>
       <c r="O16" t="n">
-        <v>4.774170710424976</v>
+        <v>4.768667938950092</v>
       </c>
       <c r="P16" t="n">
-        <v>360.6959625588568</v>
+        <v>360.6906355007882</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37017,28 +37102,28 @@
         <v>0.0732</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.006156240961702731</v>
+        <v>-0.004748494300658644</v>
       </c>
       <c r="J17" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K17" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L17" t="n">
-        <v>8.390644364075772e-05</v>
+        <v>5.018667557665779e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.171282140851605</v>
+        <v>4.16725484570928</v>
       </c>
       <c r="N17" t="n">
-        <v>25.47516715860521</v>
+        <v>25.4322071900066</v>
       </c>
       <c r="O17" t="n">
-        <v>5.047293052578303</v>
+        <v>5.043035513458794</v>
       </c>
       <c r="P17" t="n">
-        <v>354.0295475626377</v>
+        <v>354.0151500234438</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37095,28 +37180,28 @@
         <v>0.1014</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04948568191635502</v>
+        <v>0.05176466902650114</v>
       </c>
       <c r="J18" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K18" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L18" t="n">
-        <v>0.009160200400468832</v>
+        <v>0.01004211184542814</v>
       </c>
       <c r="M18" t="n">
-        <v>3.258167902001837</v>
+        <v>3.261527456339195</v>
       </c>
       <c r="N18" t="n">
-        <v>14.94084512325332</v>
+        <v>14.95343561873716</v>
       </c>
       <c r="O18" t="n">
-        <v>3.865338940281088</v>
+        <v>3.866967237867055</v>
       </c>
       <c r="P18" t="n">
-        <v>343.918940440631</v>
+        <v>343.8956324071979</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37173,28 +37258,28 @@
         <v>0.1035</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07142860339140468</v>
+        <v>0.07458886937875708</v>
       </c>
       <c r="J19" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K19" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01939300781135578</v>
+        <v>0.0211012479385454</v>
       </c>
       <c r="M19" t="n">
-        <v>3.154157868498426</v>
+        <v>3.161740058417283</v>
       </c>
       <c r="N19" t="n">
-        <v>14.61700497431442</v>
+        <v>14.67567900160038</v>
       </c>
       <c r="O19" t="n">
-        <v>3.823219189938555</v>
+        <v>3.83088488493199</v>
       </c>
       <c r="P19" t="n">
-        <v>335.2483705843794</v>
+        <v>335.2160977301826</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37251,28 +37336,28 @@
         <v>0.1228</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1772343591672979</v>
+        <v>0.179990843717781</v>
       </c>
       <c r="J20" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K20" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L20" t="n">
-        <v>0.108577599399977</v>
+        <v>0.1117116223474383</v>
       </c>
       <c r="M20" t="n">
-        <v>3.138112803084706</v>
+        <v>3.144523473558973</v>
       </c>
       <c r="N20" t="n">
-        <v>14.61178962249624</v>
+        <v>14.64795400617873</v>
       </c>
       <c r="O20" t="n">
-        <v>3.822537066203053</v>
+        <v>3.827264559209191</v>
       </c>
       <c r="P20" t="n">
-        <v>334.267320341547</v>
+        <v>334.2391709312286</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37329,28 +37414,28 @@
         <v>0.1003</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3672039225263479</v>
+        <v>0.3698662430898613</v>
       </c>
       <c r="J21" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K21" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3250326953940539</v>
+        <v>0.3286074941293151</v>
       </c>
       <c r="M21" t="n">
-        <v>3.252156575194928</v>
+        <v>3.257031663085399</v>
       </c>
       <c r="N21" t="n">
-        <v>15.86479901204355</v>
+        <v>15.89311181764606</v>
       </c>
       <c r="O21" t="n">
-        <v>3.983064023091211</v>
+        <v>3.986616587740293</v>
       </c>
       <c r="P21" t="n">
-        <v>331.2814604651799</v>
+        <v>331.25427266399</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37407,28 +37492,28 @@
         <v>0.1131</v>
       </c>
       <c r="I22" t="n">
-        <v>0.306342658508033</v>
+        <v>0.3091026950442026</v>
       </c>
       <c r="J22" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K22" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2207862852543769</v>
+        <v>0.2242700131205519</v>
       </c>
       <c r="M22" t="n">
-        <v>3.556678563463546</v>
+        <v>3.560366141888422</v>
       </c>
       <c r="N22" t="n">
-        <v>18.68172723225222</v>
+        <v>18.70800126176514</v>
       </c>
       <c r="O22" t="n">
-        <v>4.32223636931765</v>
+        <v>4.325274703618851</v>
       </c>
       <c r="P22" t="n">
-        <v>335.7560025181114</v>
+        <v>335.7277746165251</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37466,7 +37551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85871,6 +85956,123 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-38.27446915417739,178.3304063545655</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-38.27516353486383,178.33061901190015</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-38.275829058670865,178.33091881910903</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-38.27649843965286,178.3312069567088</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-38.277170144984,178.3314836904297</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-38.27782017492526,178.33181852498</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-38.27848288249677,178.3321171137054</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-38.279121942330114,178.3324998205591</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-38.27977927531849,178.33283837188515</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-38.280432187405545,178.33320281433902</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-38.28105972409457,178.3336255501069</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>-38.281666190778814,178.33409601448648</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>-38.28226271056751,178.3345891108605</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>-38.28281598114433,178.33514624953284</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>-38.2833287492775,178.33576020911977</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>-38.283830988754616,178.33638658922223</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>-38.28434260293898,178.33701213827075</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>-38.2848656689335,178.3376165050834</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>-38.28536061038573,178.3382638382129</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>-38.28579070272222,178.33898695067677</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>-38.28613078478103,178.3397823282712</t>
+        </is>
+      </c>
+      <c r="W415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
